--- a/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
+++ b/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/clients/_template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7FF892A-103F-4FE3-A81A-DF0210076B6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,9 +600,6 @@
     <t>Active Business Income</t>
   </si>
   <si>
-    <t>Excluded from Aggregate Investment Income — from a connected corporation, not portfolio.</t>
-  </si>
-  <si>
     <t>Dividends Received — Portfolio (Non-Connected)</t>
   </si>
   <si>
@@ -1657,6 +1654,9 @@
   </si>
   <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>Connected (sister corp under common control, s.186(4)): deductible under s.112, NOT active business income. Part IV = this corp's share of the payer's dividend refund - enter it in the holdco section below.</t>
   </si>
 </sst>
 </file>
@@ -2037,15 +2037,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2668,6 +2668,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="B24:D24"/>
@@ -2684,11 +2689,6 @@
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2717,7 +2717,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -2732,34 +2732,34 @@
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>143</v>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="4" spans="1:11" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" s="30" t="s">
         <v>332</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>333</v>
       </c>
       <c r="D4" s="38">
         <v>0.6</v>
@@ -2791,24 +2791,24 @@
         <v>8</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J4" s="26">
         <v>0</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="57.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="C5" s="30" t="s">
         <v>337</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>338</v>
       </c>
       <c r="D5" s="38">
         <v>0.1</v>
@@ -2826,24 +2826,24 @@
         <v>3</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J5" s="26">
         <v>95000</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="30" t="s">
         <v>342</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>343</v>
       </c>
       <c r="D6" s="38">
         <v>0</v>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J6" s="26">
         <v>0</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="39" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2961,7 +2961,7 @@
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="71" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B13" s="64"/>
       <c r="C13" s="64"/>
@@ -2976,16 +2976,16 @@
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -2994,18 +2994,18 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B15" s="26">
         <v>25000</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D15" s="30" t="s">
         <v>113</v>
@@ -3017,7 +3017,7 @@
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3116,7 +3116,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -3130,42 +3130,42 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C4" s="26">
         <v>120000</v>
@@ -3189,15 +3189,15 @@
         <v>109</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>367</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>368</v>
       </c>
       <c r="C5" s="26">
         <v>140000</v>
@@ -3221,15 +3221,15 @@
         <v>109</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>369</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>370</v>
       </c>
       <c r="C6" s="26">
         <v>90000</v>
@@ -3253,15 +3253,15 @@
         <v>109</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>371</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>372</v>
       </c>
       <c r="C7" s="26">
         <v>70000</v>
@@ -3285,15 +3285,15 @@
         <v>109</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>373</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>374</v>
       </c>
       <c r="C8" s="26">
         <v>95000</v>
@@ -3314,18 +3314,18 @@
         <v>0</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C9" s="26">
         <v>85000</v>
@@ -3346,10 +3346,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3422,7 +3422,7 @@
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B15" s="57"/>
       <c r="C15" s="57"/>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B16" s="57"/>
       <c r="C16" s="42">
@@ -3446,7 +3446,7 @@
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B17" s="57"/>
       <c r="C17" s="42">
@@ -3456,7 +3456,7 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="58" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B18" s="57"/>
       <c r="C18" s="42">
@@ -3466,7 +3466,7 @@
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B19" s="57"/>
       <c r="C19" s="34">
@@ -3475,19 +3475,19 @@
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="58" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B20" s="57"/>
       <c r="C20" s="43">
         <v>1.1499999999999999</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B21" s="57"/>
       <c r="C21" s="44">
@@ -3497,7 +3497,7 @@
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B23" s="57"/>
       <c r="C23" s="57"/>
@@ -3589,7 +3589,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="72" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B4" s="64"/>
       <c r="C4" s="24" t="s">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="72" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B5" s="64"/>
       <c r="C5" s="24" t="s">
@@ -3623,16 +3623,16 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="72" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="72" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B7" s="64"/>
       <c r="C7" s="24" t="s">
@@ -3644,8 +3644,8 @@
       <c r="C8" s="11"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
-        <v>393</v>
+      <c r="A9" s="66" t="s">
+        <v>392</v>
       </c>
       <c r="B9" s="64"/>
       <c r="C9" s="64"/>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="72" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B10" s="64"/>
       <c r="C10" s="45">
@@ -3663,20 +3663,20 @@
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="72" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B11" s="64"/>
       <c r="C11" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B12" s="64"/>
       <c r="C12" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3684,8 +3684,8 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
-        <v>398</v>
+      <c r="A14" s="66" t="s">
+        <v>397</v>
       </c>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B15" s="64"/>
       <c r="C15" s="46">
@@ -3703,7 +3703,7 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="72" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B16" s="64"/>
       <c r="C16" s="47">
@@ -3716,8 +3716,8 @@
       <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="65" t="s">
-        <v>401</v>
+      <c r="A18" s="66" t="s">
+        <v>400</v>
       </c>
       <c r="B18" s="64"/>
       <c r="C18" s="64"/>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="19" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C19" s="26">
         <v>42000</v>
@@ -3733,29 +3733,29 @@
     </row>
     <row r="20" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C20" s="26">
         <v>4000</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C21" s="26">
         <v>750</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C22" s="26">
         <v>1350</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C25" s="16">
         <f>SUM(C19:C24)</f>
@@ -3783,8 +3783,8 @@
       <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65" t="s">
-        <v>409</v>
+      <c r="A27" s="66" t="s">
+        <v>408</v>
       </c>
       <c r="B27" s="64"/>
       <c r="C27" s="64"/>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="48">
@@ -3803,7 +3803,7 @@
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C29" s="9" t="str">
         <f>IF(C28&gt;3000,"Yes - instalments likely required","No")</f>
@@ -3812,6 +3812,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:D3"/>
@@ -3821,12 +3827,6 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3872,7 +3872,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -3880,15 +3880,15 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
-        <v>414</v>
+      <c r="A4" s="63" t="s">
+        <v>413</v>
       </c>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="34">
@@ -3905,7 +3905,7 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="70" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B6" s="69"/>
       <c r="C6" s="34">
@@ -3914,7 +3914,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B7" s="69"/>
       <c r="C7" s="34">
@@ -3923,7 +3923,7 @@
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="70" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B8" s="69"/>
       <c r="C8" s="34">
@@ -3937,7 +3937,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="9" t="str">
@@ -3951,8 +3951,8 @@
       <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="65" t="s">
-        <v>420</v>
+      <c r="A12" s="66" t="s">
+        <v>419</v>
       </c>
       <c r="B12" s="64"/>
       <c r="C12" s="64"/>
@@ -3960,13 +3960,13 @@
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>143</v>
@@ -3974,24 +3974,24 @@
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B14" s="26">
         <v>10125</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B15" s="26">
         <v>10125</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4020,7 +4020,7 @@
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B20" s="16">
         <f>SUM(B14:B19)</f>
@@ -4034,8 +4034,8 @@
       <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="65" t="s">
-        <v>427</v>
+      <c r="A22" s="66" t="s">
+        <v>426</v>
       </c>
       <c r="B22" s="64"/>
       <c r="C22" s="64"/>
@@ -4043,46 +4043,46 @@
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="70" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B23" s="69"/>
       <c r="C23" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="70" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B24" s="69"/>
       <c r="C24" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="70" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B25" s="69"/>
       <c r="C25" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="70" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B26" s="69"/>
       <c r="C26" s="24" t="s">
         <v>113</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="70" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B27" s="69"/>
       <c r="C27" s="24" t="s">
@@ -4142,7 +4142,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B4" s="69"/>
       <c r="C4" s="34">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="49">
@@ -4176,14 +4176,14 @@
     </row>
     <row r="6" spans="1:4" ht="53.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B7" s="69"/>
       <c r="C7" s="34">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="70" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B8" s="69"/>
       <c r="C8" s="24" t="s">
@@ -4201,7 +4201,7 @@
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="16">
@@ -4215,16 +4215,16 @@
       <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
-        <v>442</v>
+      <c r="A11" s="66" t="s">
+        <v>441</v>
       </c>
       <c r="B11" s="64"/>
       <c r="C11" s="64"/>
       <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66" t="s">
-        <v>443</v>
+      <c r="A12" s="63" t="s">
+        <v>442</v>
       </c>
       <c r="B12" s="64"/>
       <c r="C12" s="64"/>
@@ -4232,16 +4232,16 @@
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B13" s="69"/>
       <c r="C13" s="24" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="70" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B14" s="69"/>
       <c r="C14" s="34">
@@ -4254,8 +4254,8 @@
       <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="65" t="s">
-        <v>447</v>
+      <c r="A16" s="66" t="s">
+        <v>446</v>
       </c>
       <c r="B16" s="64"/>
       <c r="C16" s="64"/>
@@ -4263,13 +4263,13 @@
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>143</v>
@@ -4287,7 +4287,7 @@
         <v>2030</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4300,17 +4300,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4349,7 +4349,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -4373,25 +4373,25 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>143</v>
@@ -4402,7 +4402,7 @@
         <v>98</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C5" s="26">
         <v>1000000</v>
@@ -4417,10 +4417,10 @@
         <v>6200</v>
       </c>
       <c r="G5" s="30" t="s">
+        <v>460</v>
+      </c>
+      <c r="H5" s="32" t="s">
         <v>461</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4455,7 +4455,7 @@
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="71" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B9" s="64"/>
       <c r="C9" s="64"/>
@@ -4467,16 +4467,16 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -4494,7 +4494,7 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="81" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4519,7 +4519,7 @@
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="71" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="81" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B15" s="64"/>
       <c r="C15" s="64"/>
@@ -4601,7 +4601,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="59" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="57"/>
@@ -4626,19 +4626,19 @@
         <v>136</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>143</v>
@@ -4658,18 +4658,18 @@
         <v>500000</v>
       </c>
       <c r="E5" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F5" s="53">
         <v>0.05</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B6" s="51">
         <v>0.27</v>
@@ -4681,18 +4681,18 @@
         <v>500000</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F6" s="53">
         <v>0.05</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="51">
         <v>0.27</v>
@@ -4704,18 +4704,18 @@
         <v>500000</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F7" s="53">
         <v>0.05</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B8" s="51">
         <v>0.27</v>
@@ -4727,18 +4727,18 @@
         <v>500000</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F8" s="53">
         <v>0.05</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B9" s="51">
         <v>0.26500000000000001</v>
@@ -4750,18 +4750,18 @@
         <v>500000</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F9" s="53">
         <v>0.13</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B10" s="51">
         <v>0.26500000000000001</v>
@@ -4773,18 +4773,18 @@
         <v>500000</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F10" s="53">
         <v>0.14974999999999999</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B11" s="51">
         <v>0.28999999999999998</v>
@@ -4796,7 +4796,7 @@
         <v>500000</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F11" s="53">
         <v>0.15</v>
@@ -4805,7 +4805,7 @@
     </row>
     <row r="12" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B12" s="51">
         <v>0.28999999999999998</v>
@@ -4817,18 +4817,18 @@
         <v>500000</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F12" s="53">
         <v>0.14000000000000001</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B13" s="51">
         <v>0.31</v>
@@ -4840,18 +4840,18 @@
         <v>500000</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F13" s="53">
         <v>0.15</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B14" s="51">
         <v>0.3</v>
@@ -4863,18 +4863,18 @@
         <v>500000</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F14" s="53">
         <v>0.15</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B15" s="51">
         <v>0.27</v>
@@ -4886,18 +4886,18 @@
         <v>500000</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F15" s="53">
         <v>0.05</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B16" s="51">
         <v>0.26500000000000001</v>
@@ -4909,7 +4909,7 @@
         <v>500000</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F16" s="53">
         <v>0.05</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B17" s="51">
         <v>0.27</v>
@@ -4930,7 +4930,7 @@
         <v>500000</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F17" s="53">
         <v>0.05</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="19" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="67" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B19" s="57"/>
       <c r="C19" s="57"/>
@@ -4972,34 +4972,34 @@
         <v>136</v>
       </c>
       <c r="B1" s="54" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="E1" s="54" t="s">
         <v>504</v>
       </c>
-      <c r="C1" s="54" t="s">
-        <v>286</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="E1" s="54" t="s">
+      <c r="F1" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>322</v>
+      </c>
+      <c r="H1" s="54" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" s="54" t="s">
         <v>505</v>
       </c>
-      <c r="F1" s="54" t="s">
-        <v>330</v>
-      </c>
-      <c r="G1" s="54" t="s">
-        <v>323</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>324</v>
-      </c>
-      <c r="I1" s="54" t="s">
+      <c r="J1" s="54" t="s">
         <v>506</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="K1" s="54" t="s">
         <v>507</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5010,211 +5010,211 @@
         <v>113</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>182</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>180</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -5254,7 +5254,7 @@
       <c r="D2" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="66" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="64"/>
@@ -5302,7 +5302,7 @@
       <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="65" t="s">
+      <c r="A10" s="66" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="64"/>
@@ -5344,7 +5344,7 @@
       <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="65" t="s">
+      <c r="A15" s="66" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="64"/>
@@ -5449,7 +5449,7 @@
       <c r="B26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="66" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="64"/>
@@ -5526,7 +5526,7 @@
       <c r="B35" s="11"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="65" t="s">
+      <c r="A36" s="66" t="s">
         <v>76</v>
       </c>
       <c r="B36" s="64"/>
@@ -5619,7 +5619,7 @@
       <c r="B46" s="11"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="65" t="s">
+      <c r="A47" s="66" t="s">
         <v>86</v>
       </c>
       <c r="B47" s="64"/>
@@ -5685,7 +5685,7 @@
       <c r="B54" s="11"/>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="65" t="s">
+      <c r="A55" s="66" t="s">
         <v>93</v>
       </c>
       <c r="B55" s="64"/>
@@ -5693,7 +5693,7 @@
       <c r="D55" s="64"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="63" t="str">
+      <c r="A56" s="65" t="str">
         <f>IF(B18&gt;0,"• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.","")</f>
         <v>• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.</v>
       </c>
@@ -5702,7 +5702,7 @@
       <c r="D56" s="64"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="63" t="str">
+      <c r="A57" s="65" t="str">
         <f>IF(COUNTIF('8. Shareholders &amp; TOSI'!I5:I20,"Not Excluded - TOSI Risk")&gt;0,"• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.","")</f>
         <v>• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.</v>
       </c>
@@ -5711,7 +5711,7 @@
       <c r="D57" s="64"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="str">
+      <c r="A58" s="65" t="str">
         <f>IF(B44&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
         <v>• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.</v>
       </c>
@@ -5720,7 +5720,7 @@
       <c r="D58" s="64"/>
     </row>
     <row r="59" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="66" t="s">
+      <c r="A59" s="63" t="s">
         <v>94</v>
       </c>
       <c r="B59" s="64"/>
@@ -5729,12 +5729,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
@@ -5742,6 +5736,12 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5989,6 +5989,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A19:B19"/>
@@ -5999,20 +6011,8 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6386,7 +6386,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="66" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="64"/>
@@ -6431,7 +6431,7 @@
       <c r="B10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="66" t="s">
         <v>158</v>
       </c>
       <c r="B11" s="64"/>
@@ -6473,7 +6473,7 @@
       <c r="B16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="66" t="s">
         <v>162</v>
       </c>
       <c r="B17" s="64"/>
@@ -6605,7 +6605,7 @@
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="66" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="64"/>
@@ -6631,15 +6631,15 @@
         <v>40000</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>182</v>
+        <v>527</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>183</v>
+        <v>535</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B37" s="30">
         <v>15000</v>
@@ -6648,12 +6648,12 @@
         <v>180</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B38" s="30">
         <v>20000</v>
@@ -6662,12 +6662,12 @@
         <v>180</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B39" s="30">
         <v>8000</v>
@@ -6676,18 +6676,18 @@
         <v>180</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B40" s="30">
         <v>0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B43" s="9">
         <f>SUM(B35:B42)</f>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B44" s="18">
         <f>B32+B43</f>
@@ -6725,8 +6725,8 @@
       <c r="B45" s="11"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="65" t="s">
-        <v>194</v>
+      <c r="A46" s="66" t="s">
+        <v>193</v>
       </c>
       <c r="B46" s="64"/>
       <c r="C46" s="64"/>
@@ -6734,7 +6734,7 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B47" s="9">
         <f>B32</f>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B48" s="9">
         <f>SUMIF(C35:C42,"Aggregate Investment Income",B35:B42)</f>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B49" s="9">
         <f>B44</f>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B51" s="55"/>
       <c r="C51" s="55"/>
@@ -6769,88 +6769,88 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B52" s="30"/>
       <c r="D52" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B53" s="30"/>
       <c r="D53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B54" s="30"/>
       <c r="D54" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="30"/>
       <c r="D55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="30"/>
       <c r="D56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" s="30"/>
       <c r="D57" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B58" s="30"/>
       <c r="D58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" s="30"/>
       <c r="D59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" s="30"/>
       <c r="D60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="55"/>
       <c r="C62" s="55"/>
@@ -6858,29 +6858,29 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B63" s="30"/>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" s="30"/>
       <c r="D64" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B65" s="30"/>
       <c r="D65" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -6930,7 +6930,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -6949,8 +6949,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
-        <v>225</v>
+      <c r="A4" s="66" t="s">
+        <v>224</v>
       </c>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -6958,7 +6958,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="26">
         <v>145000</v>
@@ -6966,7 +6966,7 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" s="26">
         <v>210000</v>
@@ -6974,7 +6974,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B7" s="26">
         <v>0</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B8" s="26">
         <v>15000</v>
@@ -6990,46 +6990,46 @@
     </row>
     <row r="9" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B9" s="26">
         <v>380000</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="26">
         <v>260000</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B11" s="26">
         <v>100000</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B12" s="26">
         <v>35000</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7042,7 +7042,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B15" s="16">
         <f>SUM(B5:B14)</f>
@@ -7054,8 +7054,8 @@
       <c r="B16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
-        <v>239</v>
+      <c r="A17" s="66" t="s">
+        <v>238</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="64"/>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B18" s="26">
         <v>95000</v>
@@ -7071,18 +7071,18 @@
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B19" s="26">
         <v>12000</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B20" s="26">
         <v>40000</v>
@@ -7090,18 +7090,18 @@
     </row>
     <row r="21" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B21" s="26">
         <v>25000</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B22" s="26">
         <v>30000</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B23" s="26">
         <v>150000</v>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B24" s="26">
         <v>20000</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B27" s="16">
         <f>SUM(B18:B26)</f>
@@ -7145,8 +7145,8 @@
       <c r="B28" s="33"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65" t="s">
-        <v>250</v>
+      <c r="A29" s="66" t="s">
+        <v>249</v>
       </c>
       <c r="B29" s="64"/>
       <c r="C29" s="64"/>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B30" s="26">
         <v>100</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B31" s="26">
         <v>90000</v>
@@ -7170,7 +7170,7 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B32" s="26">
         <v>397900</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B33" s="14">
         <f>'3. Income Statement'!B49</f>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B34" s="16">
         <f>SUM(B30:B33)</f>
@@ -7200,7 +7200,7 @@
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B36" s="16">
         <f>B27+B34</f>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B37" s="16">
         <f>B15-(B27+B34)</f>
@@ -7221,8 +7221,8 @@
       <c r="B38" s="33"/>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="65" t="s">
-        <v>258</v>
+      <c r="A39" s="66" t="s">
+        <v>257</v>
       </c>
       <c r="B39" s="64"/>
       <c r="C39" s="64"/>
@@ -7230,23 +7230,23 @@
     </row>
     <row r="40" spans="1:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B40" s="33"/>
       <c r="D40" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B41" s="16">
         <f>B15</f>
         <v>1145000</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -7278,7 +7278,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -7286,15 +7286,15 @@
     </row>
     <row r="2" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="57"/>
       <c r="D2" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
-        <v>265</v>
+      <c r="A4" s="66" t="s">
+        <v>264</v>
       </c>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -7302,14 +7302,14 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="34">
         <v>18500</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7321,7 +7321,7 @@
         <v>42300</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7330,8 +7330,8 @@
       <c r="C7" s="11"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65" t="s">
-        <v>269</v>
+      <c r="A8" s="66" t="s">
+        <v>268</v>
       </c>
       <c r="B8" s="64"/>
       <c r="C8" s="64"/>
@@ -7339,14 +7339,14 @@
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B9" s="69"/>
       <c r="C9" s="34">
         <v>65000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7355,8 +7355,8 @@
       <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
-        <v>272</v>
+      <c r="A11" s="66" t="s">
+        <v>271</v>
       </c>
       <c r="B11" s="64"/>
       <c r="C11" s="64"/>
@@ -7364,14 +7364,14 @@
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="70" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B12" s="69"/>
       <c r="C12" s="34">
         <v>22000</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7380,8 +7380,8 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
-        <v>275</v>
+      <c r="A14" s="66" t="s">
+        <v>274</v>
       </c>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
@@ -7389,13 +7389,13 @@
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>143</v>
@@ -7443,8 +7443,8 @@
       <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="65" t="s">
-        <v>278</v>
+      <c r="A21" s="66" t="s">
+        <v>277</v>
       </c>
       <c r="B21" s="64"/>
       <c r="C21" s="64"/>
@@ -7452,7 +7452,7 @@
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>152</v>
@@ -7478,8 +7478,8 @@
       <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="65" t="s">
-        <v>279</v>
+      <c r="A26" s="66" t="s">
+        <v>278</v>
       </c>
       <c r="B26" s="64"/>
       <c r="C26" s="64"/>
@@ -7487,19 +7487,19 @@
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="70" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="69"/>
       <c r="C27" s="34">
         <v>0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="70" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B28" s="69"/>
       <c r="C28" s="34">
@@ -7508,15 +7508,21 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" s="34"/>
       <c r="D30" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
@@ -7525,12 +7531,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7557,7 +7557,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -7571,31 +7571,31 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>143</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="4" spans="1:10" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B4" s="5">
         <v>180000</v>
@@ -7633,12 +7633,12 @@
         <v>172800</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B5" s="5">
         <v>45000</v>
@@ -7668,12 +7668,12 @@
         <v>46800</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B6" s="5">
         <v>22000</v>
@@ -7706,7 +7706,7 @@
     </row>
     <row r="7" spans="1:10" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B7" s="5">
         <v>8000</v>
@@ -7736,12 +7736,12 @@
         <v>10349.999999999998</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B8" s="5">
         <v>5000</v>
@@ -7771,7 +7771,7 @@
         <v>4750</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7889,7 +7889,7 @@
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="67" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B15" s="57"/>
       <c r="C15" s="57"/>
@@ -7976,7 +7976,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="2" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="59" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="57"/>
@@ -7998,22 +7998,22 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>143</v>
@@ -8021,10 +8021,10 @@
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>313</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>314</v>
       </c>
       <c r="C5" s="38">
         <v>1</v>
@@ -8041,15 +8041,15 @@
         <v>350000</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>316</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>317</v>
       </c>
       <c r="C6" s="38">
         <v>1</v>
@@ -8064,7 +8064,7 @@
         <v>150000</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8116,7 +8116,7 @@
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B13" s="69"/>
       <c r="C13" s="24" t="s">

--- a/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
+++ b/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/clients/_template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7FF892A-103F-4FE3-A81A-DF0210076B6E}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DF8D4F-B7D7-4381-B990-F12280691290}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="538">
   <si>
     <t>CCPC Corporate Tax Planning &amp; Compliance Intake Workbook</t>
   </si>
@@ -1657,6 +1657,12 @@
   </si>
   <si>
     <t>Connected (sister corp under common control, s.186(4)): deductible under s.112, NOT active business income. Part IV = this corp's share of the payer's dividend refund - enter it in the holdco section below.</t>
+  </si>
+  <si>
+    <t>Refundable Portion of SR&amp;ED ITC ($)</t>
+  </si>
+  <si>
+    <t>Cash-refundable part of the ITC (s.127.1). Defaults to the full ITC when the enhanced 35% rate applies (current expenditures of a CCPC under the expenditure limit). Overwrite with the actual refundable amount if part is non-refundable.</t>
   </si>
 </sst>
 </file>
@@ -2037,15 +2043,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2155,6 +2161,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2668,11 +2678,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="B24:D24"/>
@@ -2689,6 +2694,11 @@
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3644,7 +3654,7 @@
       <c r="C8" s="11"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="65" t="s">
         <v>392</v>
       </c>
       <c r="B9" s="64"/>
@@ -3684,7 +3694,7 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="65" t="s">
         <v>397</v>
       </c>
       <c r="B14" s="64"/>
@@ -3716,7 +3726,7 @@
       <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="65" t="s">
         <v>400</v>
       </c>
       <c r="B18" s="64"/>
@@ -3783,7 +3793,7 @@
       <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="65" t="s">
         <v>408</v>
       </c>
       <c r="B27" s="64"/>
@@ -3812,12 +3822,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:D3"/>
@@ -3827,6 +3831,12 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3887,7 +3897,7 @@
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="66" t="s">
         <v>413</v>
       </c>
       <c r="B4" s="64"/>
@@ -3951,7 +3961,7 @@
       <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="65" t="s">
         <v>419</v>
       </c>
       <c r="B12" s="64"/>
@@ -4034,7 +4044,7 @@
       <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="65" t="s">
         <v>426</v>
       </c>
       <c r="B22" s="64"/>
@@ -4210,12 +4220,20 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
+      <c r="A10" s="17" t="s">
+        <v>536</v>
+      </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="C10" s="16">
+        <f>IF(C8="Yes",C9,0)</f>
+        <v>22750</v>
+      </c>
+      <c r="D10" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="65" t="s">
         <v>441</v>
       </c>
       <c r="B11" s="64"/>
@@ -4223,7 +4241,7 @@
       <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="66" t="s">
         <v>442</v>
       </c>
       <c r="B12" s="64"/>
@@ -4254,7 +4272,7 @@
       <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="65" t="s">
         <v>446</v>
       </c>
       <c r="B16" s="64"/>
@@ -4300,17 +4318,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5254,7 +5272,7 @@
       <c r="D2" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="64"/>
@@ -5302,7 +5320,7 @@
       <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="65" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="64"/>
@@ -5344,7 +5362,7 @@
       <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="65" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="64"/>
@@ -5449,7 +5467,7 @@
       <c r="B26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="65" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="64"/>
@@ -5526,7 +5544,7 @@
       <c r="B35" s="11"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="65" t="s">
         <v>76</v>
       </c>
       <c r="B36" s="64"/>
@@ -5619,7 +5637,7 @@
       <c r="B46" s="11"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="65" t="s">
         <v>86</v>
       </c>
       <c r="B47" s="64"/>
@@ -5685,7 +5703,7 @@
       <c r="B54" s="11"/>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="66" t="s">
+      <c r="A55" s="65" t="s">
         <v>93</v>
       </c>
       <c r="B55" s="64"/>
@@ -5693,7 +5711,7 @@
       <c r="D55" s="64"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="65" t="str">
+      <c r="A56" s="63" t="str">
         <f>IF(B18&gt;0,"• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.","")</f>
         <v>• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.</v>
       </c>
@@ -5702,7 +5720,7 @@
       <c r="D56" s="64"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="65" t="str">
+      <c r="A57" s="63" t="str">
         <f>IF(COUNTIF('8. Shareholders &amp; TOSI'!I5:I20,"Not Excluded - TOSI Risk")&gt;0,"• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.","")</f>
         <v>• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.</v>
       </c>
@@ -5711,7 +5729,7 @@
       <c r="D57" s="64"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="65" t="str">
+      <c r="A58" s="63" t="str">
         <f>IF(B44&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
         <v>• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.</v>
       </c>
@@ -5720,7 +5738,7 @@
       <c r="D58" s="64"/>
     </row>
     <row r="59" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="63" t="s">
+      <c r="A59" s="66" t="s">
         <v>94</v>
       </c>
       <c r="B59" s="64"/>
@@ -5729,6 +5747,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
@@ -5736,12 +5760,6 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5989,6 +6007,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A5:B5"/>
@@ -6001,18 +6031,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6386,7 +6404,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="64"/>
@@ -6431,7 +6449,7 @@
       <c r="B10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="65" t="s">
         <v>158</v>
       </c>
       <c r="B11" s="64"/>
@@ -6473,7 +6491,7 @@
       <c r="B16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="65" t="s">
         <v>162</v>
       </c>
       <c r="B17" s="64"/>
@@ -6605,7 +6623,7 @@
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="65" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="64"/>
@@ -6725,7 +6743,7 @@
       <c r="B45" s="11"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="65" t="s">
         <v>193</v>
       </c>
       <c r="B46" s="64"/>
@@ -6949,7 +6967,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>224</v>
       </c>
       <c r="B4" s="64"/>
@@ -7054,7 +7072,7 @@
       <c r="B16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="65" t="s">
         <v>238</v>
       </c>
       <c r="B17" s="64"/>
@@ -7145,7 +7163,7 @@
       <c r="B28" s="33"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="65" t="s">
         <v>249</v>
       </c>
       <c r="B29" s="64"/>
@@ -7221,7 +7239,7 @@
       <c r="B38" s="33"/>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="65" t="s">
         <v>257</v>
       </c>
       <c r="B39" s="64"/>
@@ -7293,7 +7311,7 @@
       <c r="D2" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>264</v>
       </c>
       <c r="B4" s="64"/>
@@ -7330,7 +7348,7 @@
       <c r="C7" s="11"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="65" t="s">
         <v>268</v>
       </c>
       <c r="B8" s="64"/>
@@ -7355,7 +7373,7 @@
       <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="65" t="s">
         <v>271</v>
       </c>
       <c r="B11" s="64"/>
@@ -7380,7 +7398,7 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="65" t="s">
         <v>274</v>
       </c>
       <c r="B14" s="64"/>
@@ -7443,7 +7461,7 @@
       <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="65" t="s">
         <v>277</v>
       </c>
       <c r="B21" s="64"/>
@@ -7478,7 +7496,7 @@
       <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="65" t="s">
         <v>278</v>
       </c>
       <c r="B26" s="64"/>
@@ -7517,12 +7535,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
@@ -7531,6 +7543,12 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
+++ b/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/clients/_template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DF8D4F-B7D7-4381-B990-F12280691290}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D5721EB-262C-459F-B22F-6D0592710C65}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="540">
   <si>
     <t>CCPC Corporate Tax Planning &amp; Compliance Intake Workbook</t>
   </si>
@@ -1663,6 +1663,12 @@
   </si>
   <si>
     <t>Cash-refundable part of the ITC (s.127.1). Defaults to the full ITC when the enhanced 35% rate applies (current expenditures of a CCPC under the expenditure limit). Overwrite with the actual refundable amount if part is non-refundable.</t>
+  </si>
+  <si>
+    <t>Refundable Portion of Provincial Credit ($)</t>
+  </si>
+  <si>
+    <t>Part of the provincial credit paid in cash even with no tax owing (e.g., Alberta Innovation Employment Grant). Leave blank if non-refundable - unused amounts then carry forward.</t>
   </si>
 </sst>
 </file>
@@ -2043,15 +2049,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2678,6 +2684,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="B24:D24"/>
@@ -2694,11 +2705,6 @@
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3654,7 +3660,7 @@
       <c r="C8" s="11"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="66" t="s">
         <v>392</v>
       </c>
       <c r="B9" s="64"/>
@@ -3694,7 +3700,7 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="66" t="s">
         <v>397</v>
       </c>
       <c r="B14" s="64"/>
@@ -3726,7 +3732,7 @@
       <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="66" t="s">
         <v>400</v>
       </c>
       <c r="B18" s="64"/>
@@ -3793,7 +3799,7 @@
       <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="66" t="s">
         <v>408</v>
       </c>
       <c r="B27" s="64"/>
@@ -3822,6 +3828,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:D3"/>
@@ -3831,12 +3843,6 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3897,7 +3903,7 @@
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="63" t="s">
         <v>413</v>
       </c>
       <c r="B4" s="64"/>
@@ -3961,7 +3967,7 @@
       <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="66" t="s">
         <v>419</v>
       </c>
       <c r="B12" s="64"/>
@@ -4044,7 +4050,7 @@
       <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="66" t="s">
         <v>426</v>
       </c>
       <c r="B22" s="64"/>
@@ -4233,7 +4239,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="66" t="s">
         <v>441</v>
       </c>
       <c r="B11" s="64"/>
@@ -4241,7 +4247,7 @@
       <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="63" t="s">
         <v>442</v>
       </c>
       <c r="B12" s="64"/>
@@ -4267,12 +4273,17 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
+      <c r="A15" s="70" t="s">
+        <v>538</v>
+      </c>
+      <c r="B15" s="69"/>
+      <c r="C15" s="34"/>
+      <c r="D15" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="66" t="s">
         <v>446</v>
       </c>
       <c r="B16" s="64"/>
@@ -4317,18 +4328,19 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A8:B8"/>
+  <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5272,7 +5284,7 @@
       <c r="D2" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="66" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="64"/>
@@ -5320,7 +5332,7 @@
       <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="65" t="s">
+      <c r="A10" s="66" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="64"/>
@@ -5362,7 +5374,7 @@
       <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="65" t="s">
+      <c r="A15" s="66" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="64"/>
@@ -5467,7 +5479,7 @@
       <c r="B26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="66" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="64"/>
@@ -5544,7 +5556,7 @@
       <c r="B35" s="11"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="65" t="s">
+      <c r="A36" s="66" t="s">
         <v>76</v>
       </c>
       <c r="B36" s="64"/>
@@ -5637,7 +5649,7 @@
       <c r="B46" s="11"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="65" t="s">
+      <c r="A47" s="66" t="s">
         <v>86</v>
       </c>
       <c r="B47" s="64"/>
@@ -5703,7 +5715,7 @@
       <c r="B54" s="11"/>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="65" t="s">
+      <c r="A55" s="66" t="s">
         <v>93</v>
       </c>
       <c r="B55" s="64"/>
@@ -5711,7 +5723,7 @@
       <c r="D55" s="64"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="63" t="str">
+      <c r="A56" s="65" t="str">
         <f>IF(B18&gt;0,"• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.","")</f>
         <v>• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.</v>
       </c>
@@ -5720,7 +5732,7 @@
       <c r="D56" s="64"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="63" t="str">
+      <c r="A57" s="65" t="str">
         <f>IF(COUNTIF('8. Shareholders &amp; TOSI'!I5:I20,"Not Excluded - TOSI Risk")&gt;0,"• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.","")</f>
         <v>• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.</v>
       </c>
@@ -5729,7 +5741,7 @@
       <c r="D57" s="64"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="str">
+      <c r="A58" s="65" t="str">
         <f>IF(B44&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
         <v>• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.</v>
       </c>
@@ -5738,7 +5750,7 @@
       <c r="D58" s="64"/>
     </row>
     <row r="59" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="66" t="s">
+      <c r="A59" s="63" t="s">
         <v>94</v>
       </c>
       <c r="B59" s="64"/>
@@ -5747,12 +5759,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
@@ -5760,6 +5766,12 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6007,6 +6019,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A19:B19"/>
@@ -6019,18 +6043,6 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6404,7 +6416,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="66" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="64"/>
@@ -6449,7 +6461,7 @@
       <c r="B10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="66" t="s">
         <v>158</v>
       </c>
       <c r="B11" s="64"/>
@@ -6491,7 +6503,7 @@
       <c r="B16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="66" t="s">
         <v>162</v>
       </c>
       <c r="B17" s="64"/>
@@ -6623,7 +6635,7 @@
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="66" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="64"/>
@@ -6743,7 +6755,7 @@
       <c r="B45" s="11"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="66" t="s">
         <v>193</v>
       </c>
       <c r="B46" s="64"/>
@@ -6967,7 +6979,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="66" t="s">
         <v>224</v>
       </c>
       <c r="B4" s="64"/>
@@ -7072,7 +7084,7 @@
       <c r="B16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="66" t="s">
         <v>238</v>
       </c>
       <c r="B17" s="64"/>
@@ -7163,7 +7175,7 @@
       <c r="B28" s="33"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="66" t="s">
         <v>249</v>
       </c>
       <c r="B29" s="64"/>
@@ -7239,7 +7251,7 @@
       <c r="B38" s="33"/>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="65" t="s">
+      <c r="A39" s="66" t="s">
         <v>257</v>
       </c>
       <c r="B39" s="64"/>
@@ -7311,7 +7323,7 @@
       <c r="D2" s="57"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="66" t="s">
         <v>264</v>
       </c>
       <c r="B4" s="64"/>
@@ -7348,7 +7360,7 @@
       <c r="C7" s="11"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="66" t="s">
         <v>268</v>
       </c>
       <c r="B8" s="64"/>
@@ -7373,7 +7385,7 @@
       <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="66" t="s">
         <v>271</v>
       </c>
       <c r="B11" s="64"/>
@@ -7398,7 +7410,7 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="66" t="s">
         <v>274</v>
       </c>
       <c r="B14" s="64"/>
@@ -7461,7 +7473,7 @@
       <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="65" t="s">
+      <c r="A21" s="66" t="s">
         <v>277</v>
       </c>
       <c r="B21" s="64"/>
@@ -7496,7 +7508,7 @@
       <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="66" t="s">
         <v>278</v>
       </c>
       <c r="B26" s="64"/>
@@ -7535,6 +7547,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
@@ -7543,12 +7561,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
+++ b/clients/_template/CCPC_Tax_Planning_Intake_Workbook.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/clients/_template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhd_s\AppData\Local\Temp\claude\C--Users-mhd-s-OneDrive-Google-Drive-Docs-Biz-Infograph-Claude-tax-planning-agent-rate-llm\e972fdae-35b9-403a-9197-7df442a6acba\scratchpad\dash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_44A903A2E52269CB727786B3BF84C54966D86C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D5721EB-262C-459F-B22F-6D0592710C65}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C832AFBE-7381-4DFE-B124-3B8DECD38CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="581">
   <si>
     <t>CCPC Corporate Tax Planning &amp; Compliance Intake Workbook</t>
   </si>
@@ -225,12 +225,6 @@
     <t>Net Active Business Income (this entity)</t>
   </si>
   <si>
-    <t>Aggregate Investment Income (this entity, current year — used as proxy for prior-year AAII test)</t>
-  </si>
-  <si>
-    <t>Passive-Income Grind (reduction to $500K limit: 5 × (AAII − $50,000), capped)</t>
-  </si>
-  <si>
     <t>Group Taxable Capital Employed in Canada (from Associated Corporations tab)</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>This Entity's SBD Limit (lesser of grind-adjusted limit and Schedule 23 allocation)</t>
   </si>
   <si>
-    <t>If associated, pulls this entity's row from the Schedule 23 allocation table by name; if not associated, defaults to the full $500K (post-grind).</t>
-  </si>
-  <si>
     <t>Active Business Income Taxed at SBD Rate</t>
   </si>
   <si>
@@ -255,21 +246,12 @@
     <t>⚠ Passive-Income Grind Flag</t>
   </si>
   <si>
-    <t>2. CURRENT-YEAR CORPORATE TAX ESTIMATE (federal + provincial)</t>
-  </si>
-  <si>
     <t>Tax on SBD-Rate Income</t>
   </si>
   <si>
     <t>Tax on General-Rate Active Business Income</t>
   </si>
   <si>
-    <t>Tax on Aggregate Investment Income</t>
-  </si>
-  <si>
-    <t>ESTIMATED TOTAL CORPORATE TAX PAYABLE</t>
-  </si>
-  <si>
     <t>Less: Instalments Already Paid</t>
   </si>
   <si>
@@ -279,39 +261,18 @@
     <t>Instalments Likely Required Next Year?</t>
   </si>
   <si>
-    <t>3. RDTOH / GRIP / CDA — RECOVERABLE TAX POOLS</t>
-  </si>
-  <si>
-    <t>Non-Eligible RDTOH Addition This Year (≈30⅔% of Aggregate Investment Income)</t>
-  </si>
-  <si>
     <t>Non-Eligible RDTOH — Opening Balance</t>
   </si>
   <si>
-    <t>Non-Eligible RDTOH — Closing Balance (Opening + Addition)</t>
-  </si>
-  <si>
-    <t>Eligible RDTOH — Opening/Closing Balance (carried forward)</t>
-  </si>
-  <si>
     <t>Non-Eligible Dividend Needed to Fully Recover Non-Eligible RDTOH (÷38⅓%)</t>
   </si>
   <si>
     <t>Eligible Dividend Needed to Fully Recover Eligible RDTOH (÷38⅓%)</t>
   </si>
   <si>
-    <t>GRIP Balance Available (for lower-taxed ELIGIBLE dividends)</t>
-  </si>
-  <si>
-    <t>CDA Balance Available (paid 100% TAX-FREE by election — T2054)</t>
-  </si>
-  <si>
     <t>⚠ Action Flag</t>
   </si>
   <si>
-    <t>4. PAYROLL, GST/HST &amp; COMPLIANCE SUMMARY</t>
-  </si>
-  <si>
     <t>Total Salaries &amp; Wages Paid</t>
   </si>
   <si>
@@ -324,15 +285,9 @@
     <t>CCA Claimed This Year (reduces taxable income above — apply manually if not yet reflected)</t>
   </si>
   <si>
-    <t>SR&amp;ED Investment Tax Credit Estimate</t>
-  </si>
-  <si>
     <t>Provincial Credit Estimate</t>
   </si>
   <si>
-    <t>5. PLANNING FLAGS TO DISCUSS WITH YOUR ACCOUNTANT</t>
-  </si>
-  <si>
     <t>• Salary vs. dividend mix for each owner-manager should be modelled against personal marginal rates (see the separate Personal Tax module) — corporate tax alone does not determine the optimal mix.</t>
   </si>
   <si>
@@ -1669,6 +1624,174 @@
   </si>
   <si>
     <t>Part of the provincial credit paid in cash even with no tax owing (e.g., Alberta Innovation Employment Grant). Leave blank if non-refundable - unused amounts then carry forward.</t>
+  </si>
+  <si>
+    <t>Adjusted Aggregate Investment Income (current year — Part I investment income + portfolio dividends)</t>
+  </si>
+  <si>
+    <t>Connected-corporation dividends are excluded. The grind below uses the PRIOR-year figure from '5. Prior-Year Tax Attributes' when entered.</t>
+  </si>
+  <si>
+    <t>Passive-Income Grind (5 × (prior-year adjusted AAII − $50,000), capped; current year used as proxy if prior year blank)</t>
+  </si>
+  <si>
+    <t>If associated, pulls this entity's Schedule 23 allocation by matching its legal name (from Entity Setup) on the Associated Corporations tab; if not found or not associated, defaults to the full $500K (post-grind).</t>
+  </si>
+  <si>
+    <t>2. INVESTMENT INCOME &amp; PART IV TAX</t>
+  </si>
+  <si>
+    <t>Investment-Income Detail Supplied? (holdco section, '3. Income Statement')</t>
+  </si>
+  <si>
+    <t>If No, the single Aggregate Investment Income figure is used for everything below.</t>
+  </si>
+  <si>
+    <t>Part I Investment Income (interest, rents, taxable capital gains)</t>
+  </si>
+  <si>
+    <t>Dividends received are deductible (s.112) and excluded here.</t>
+  </si>
+  <si>
+    <t>Portfolio Dividends Received (non-connected)</t>
+  </si>
+  <si>
+    <t>Connected-Corporation Dividends Received</t>
+  </si>
+  <si>
+    <t>Part IV Tax on Portfolio Dividends (38⅓%)</t>
+  </si>
+  <si>
+    <t>Part IV Tax on Connected Dividends (share of payer's refund)</t>
+  </si>
+  <si>
+    <t>TOTAL PART IV TAX (refundable — added to RDTOH)</t>
+  </si>
+  <si>
+    <t>Non-Taxable Capital Gains (credits the CDA)</t>
+  </si>
+  <si>
+    <t>Equals the taxable portion at a 1/2 inclusion rate.</t>
+  </si>
+  <si>
+    <t>3. CURRENT-YEAR CORPORATE TAX ESTIMATE (federal + provincial)</t>
+  </si>
+  <si>
+    <t>Tax on Part I Investment Income</t>
+  </si>
+  <si>
+    <t>PART I TAX (before credits)</t>
+  </si>
+  <si>
+    <t>Part IV Tax</t>
+  </si>
+  <si>
+    <t>Part III.1 Tax — excessive eligible dividend (20%, if no election)</t>
+  </si>
+  <si>
+    <t>Avoidable by the s.185.1(2) election to treat the excess as non-eligible.</t>
+  </si>
+  <si>
+    <t>Part III Tax — excessive capital dividend (60%, if no election)</t>
+  </si>
+  <si>
+    <t>Avoidable by the s.184(3) election to treat the excess as a taxable dividend.</t>
+  </si>
+  <si>
+    <t>TOTAL TAX PAYABLE BEFORE DIVIDEND REFUND</t>
+  </si>
+  <si>
+    <t>Less: Dividend Refund</t>
+  </si>
+  <si>
+    <t>Less: Credits Applied Against Part I Tax (never below zero)</t>
+  </si>
+  <si>
+    <t>SR&amp;ED ITC + provincial credit reduce Part I tax only — not Part IV, III.1 or III.</t>
+  </si>
+  <si>
+    <t>Less: Refundable Credits Paid in Cash (excess over Part I tax)</t>
+  </si>
+  <si>
+    <t>Paid only once the SR&amp;ED / provincial claim is accepted.</t>
+  </si>
+  <si>
+    <t>NET CORPORATE TAX AFTER CREDITS</t>
+  </si>
+  <si>
+    <t>Unused Non-Refundable Credits (carry forward — NOT in the balance above)</t>
+  </si>
+  <si>
+    <t>4. RDTOH / GRIP / CDA — RECOVERABLE TAX POOLS</t>
+  </si>
+  <si>
+    <t>Non-Eligible RDTOH Addition (30⅔% of Part I investment income + non-eligible Part IV)</t>
+  </si>
+  <si>
+    <t>Non-Eligible RDTOH — Year-End, Before Dividends</t>
+  </si>
+  <si>
+    <t>Eligible RDTOH Addition (eligible portfolio Part IV + connected Part IV from payer's eligible RDTOH)</t>
+  </si>
+  <si>
+    <t>Eligible RDTOH — Year-End, Before Dividends</t>
+  </si>
+  <si>
+    <t>GRIP Addition (0.72 × general-rate ABI + eligible dividends received)</t>
+  </si>
+  <si>
+    <t>GRIP Available at Year-End</t>
+  </si>
+  <si>
+    <t>CDA Addition (non-taxable capital gains + life insurance over ACB)</t>
+  </si>
+  <si>
+    <t>CDA Available at Year-End</t>
+  </si>
+  <si>
+    <t>5. DIVIDENDS PAID THIS YEAR — REFUND &amp; DESIGNATION TESTS</t>
+  </si>
+  <si>
+    <t>Capital Dividends Paid</t>
+  </si>
+  <si>
+    <t>Refund from Non-Eligible RDTOH (non-eligible dividends × 38⅓%)</t>
+  </si>
+  <si>
+    <t>Refund from Eligible RDTOH (eligible dividends, then non-eligible overflow)</t>
+  </si>
+  <si>
+    <t>Eligible dividends recover eligible RDTOH only; non-eligible dividends use non-eligible RDTOH first.</t>
+  </si>
+  <si>
+    <t>TOTAL DIVIDEND REFUND</t>
+  </si>
+  <si>
+    <t>Non-Eligible RDTOH Carried Forward</t>
+  </si>
+  <si>
+    <t>Eligible RDTOH Carried Forward</t>
+  </si>
+  <si>
+    <t>Excessive Eligible Dividend Designation (eligible paid over GRIP)</t>
+  </si>
+  <si>
+    <t>GRIP Carried Forward</t>
+  </si>
+  <si>
+    <t>Excessive Capital Dividend (capital paid over CDA)</t>
+  </si>
+  <si>
+    <t>CDA Carried Forward</t>
+  </si>
+  <si>
+    <t>6. PAYROLL, GST/HST &amp; COMPLIANCE SUMMARY</t>
+  </si>
+  <si>
+    <t>SR&amp;ED Investment Tax Credit Estimate (of which refundable: see Credits tab)</t>
+  </si>
+  <si>
+    <t>7. PLANNING FLAGS TO DISCUSS WITH YOUR ACCOUNTANT</t>
   </si>
 </sst>
 </file>
@@ -1696,66 +1819,66 @@
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1953,7 +2076,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1985,7 +2108,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2049,15 +2171,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2084,6 +2206,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2167,10 +2301,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2364,142 +2494,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="57"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="57"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="57"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -2515,69 +2645,69 @@
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -2655,40 +2785,35 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="57"/>
-      <c r="C48" s="57"/>
-      <c r="D48" s="57"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="59" t="s">
+      <c r="A49" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="57"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="57"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
+      <c r="A50" s="56"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="B24:D24"/>
@@ -2705,6 +2830,11 @@
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2732,221 +2862,221 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>320</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="D4" s="37">
+        <v>0.6</v>
+      </c>
+      <c r="E4" s="37">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="29">
+        <v>44</v>
+      </c>
+      <c r="G4" s="29">
+        <v>45</v>
+      </c>
+      <c r="H4" s="29">
+        <v>8</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" s="25">
+        <v>0</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="57.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C5" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D5" s="37">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="37">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="29">
+        <v>42</v>
+      </c>
+      <c r="G5" s="29">
+        <v>5</v>
+      </c>
+      <c r="H5" s="29">
+        <v>3</v>
+      </c>
+      <c r="I5" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="J5" s="25">
+        <v>95000</v>
+      </c>
+      <c r="K5" s="31" t="s">
         <v>324</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B6" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="C6" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="D6" s="37">
+        <v>0</v>
+      </c>
+      <c r="E6" s="37">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29">
+        <v>0</v>
+      </c>
+      <c r="H6" s="29">
+        <v>0</v>
+      </c>
+      <c r="I6" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J6" s="25">
+        <v>0</v>
+      </c>
+      <c r="K6" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="D4" s="38">
-        <v>0.6</v>
-      </c>
-      <c r="E4" s="38">
-        <v>0.6</v>
-      </c>
-      <c r="F4" s="30">
-        <v>44</v>
-      </c>
-      <c r="G4" s="30">
-        <v>45</v>
-      </c>
-      <c r="H4" s="30">
-        <v>8</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="J4" s="26">
-        <v>0</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="57.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="30">
-        <v>42</v>
-      </c>
-      <c r="G5" s="30">
-        <v>5</v>
-      </c>
-      <c r="H5" s="30">
-        <v>3</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="J5" s="26">
-        <v>95000</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="38">
-        <v>0</v>
-      </c>
-      <c r="E6" s="38">
-        <v>0.3</v>
-      </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30">
-        <v>0</v>
-      </c>
-      <c r="H6" s="30">
-        <v>0</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="J6" s="26">
-        <v>0</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>344</v>
-      </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="28"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="27"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="28"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="27"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="28"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" spans="1:11" ht="53.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="41">
+      <c r="D11" s="40">
         <f>SUM(D4:D10)</f>
         <v>0.7</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="40">
         <f>SUM(E4:E10)</f>
         <v>1</v>
       </c>
@@ -2958,8 +3088,8 @@
         <v>1 shareholder(s) flagged for TOSI risk</v>
       </c>
       <c r="J11" s="11"/>
-      <c r="K11" s="39" t="s">
-        <v>345</v>
+      <c r="K11" s="38" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2976,32 +3106,32 @@
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71" t="s">
-        <v>346</v>
-      </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="69"/>
+      <c r="A13" s="70" t="s">
+        <v>331</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -3010,21 +3140,21 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="B15" s="26">
+      <c r="A15" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="25">
         <v>25000</v>
       </c>
-      <c r="C15" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>113</v>
+      <c r="C15" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>98</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
@@ -3033,34 +3163,34 @@
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="22" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
-      <c r="K16" s="28"/>
+      <c r="K16" s="27"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
-      <c r="K17" s="28"/>
+      <c r="K17" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3131,282 +3261,282 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="25">
+        <v>120000</v>
+      </c>
+      <c r="D4" s="25">
+        <v>3867.5</v>
+      </c>
+      <c r="E4" s="25">
+        <v>396</v>
+      </c>
+      <c r="F4" s="25">
+        <v>0</v>
+      </c>
+      <c r="G4" s="25">
+        <v>28000</v>
+      </c>
+      <c r="H4" s="25">
+        <v>6000</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="25">
+        <v>140000</v>
+      </c>
+      <c r="D5" s="25">
+        <v>3867.5</v>
+      </c>
+      <c r="E5" s="25">
+        <v>396</v>
+      </c>
+      <c r="F5" s="25">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G5" s="25">
+        <v>30000</v>
+      </c>
+      <c r="H5" s="25">
+        <v>0</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C6" s="25">
+        <v>90000</v>
+      </c>
+      <c r="D6" s="25">
+        <v>3867.5</v>
+      </c>
+      <c r="E6" s="25">
+        <v>396</v>
+      </c>
+      <c r="F6" s="25">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G6" s="25">
+        <v>17100</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B7" s="29" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C7" s="25">
+        <v>70000</v>
+      </c>
+      <c r="D7" s="25">
+        <v>3867.5</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="25">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G7" s="25">
+        <v>11900</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B8" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="C8" s="25">
+        <v>95000</v>
+      </c>
+      <c r="D8" s="25">
+        <v>3867.5</v>
+      </c>
+      <c r="E8" s="25">
+        <v>396</v>
+      </c>
+      <c r="F8" s="25">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G8" s="25">
+        <v>18500</v>
+      </c>
+      <c r="H8" s="25">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="J8" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="C4" s="26">
-        <v>120000</v>
-      </c>
-      <c r="D4" s="26">
+      <c r="B9" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="25">
+        <v>85000</v>
+      </c>
+      <c r="D9" s="25">
         <v>3867.5</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E9" s="25">
         <v>396</v>
       </c>
-      <c r="F4" s="26">
-        <v>0</v>
-      </c>
-      <c r="G4" s="26">
-        <v>28000</v>
-      </c>
-      <c r="H4" s="26">
-        <v>6000</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="C5" s="26">
-        <v>140000</v>
-      </c>
-      <c r="D5" s="26">
-        <v>3867.5</v>
-      </c>
-      <c r="E5" s="26">
-        <v>396</v>
-      </c>
-      <c r="F5" s="26">
+      <c r="F9" s="25">
         <v>1049.1199999999999</v>
       </c>
-      <c r="G5" s="26">
-        <v>30000</v>
-      </c>
-      <c r="H5" s="26">
-        <v>0</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>368</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="C6" s="26">
-        <v>90000</v>
-      </c>
-      <c r="D6" s="26">
-        <v>3867.5</v>
-      </c>
-      <c r="E6" s="26">
-        <v>396</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G6" s="26">
-        <v>17100</v>
-      </c>
-      <c r="H6" s="26">
-        <v>0</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="C7" s="26">
-        <v>70000</v>
-      </c>
-      <c r="D7" s="26">
-        <v>3867.5</v>
-      </c>
-      <c r="E7" s="26">
-        <v>0</v>
-      </c>
-      <c r="F7" s="26">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G7" s="26">
-        <v>11900</v>
-      </c>
-      <c r="H7" s="26">
-        <v>0</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="C8" s="26">
-        <v>95000</v>
-      </c>
-      <c r="D8" s="26">
-        <v>3867.5</v>
-      </c>
-      <c r="E8" s="26">
-        <v>396</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G8" s="26">
-        <v>18500</v>
-      </c>
-      <c r="H8" s="26">
-        <v>0</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="C9" s="26">
-        <v>85000</v>
-      </c>
-      <c r="D9" s="26">
-        <v>3867.5</v>
-      </c>
-      <c r="E9" s="26">
-        <v>396</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25">
         <v>15700</v>
       </c>
-      <c r="H9" s="26">
-        <v>0</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>365</v>
+      <c r="H9" s="25">
+        <v>0</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="16">
@@ -3437,117 +3567,117 @@
       <c r="J13" s="11"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56" t="s">
-        <v>376</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
+      <c r="A15" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
-        <v>377</v>
-      </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="42">
+      <c r="A16" s="57" t="s">
+        <v>362</v>
+      </c>
+      <c r="B16" s="56"/>
+      <c r="C16" s="41">
         <f>D13</f>
         <v>23205</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
-        <v>378</v>
-      </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="42">
+      <c r="A17" s="57" t="s">
+        <v>363</v>
+      </c>
+      <c r="B17" s="56"/>
+      <c r="C17" s="41">
         <f>E13</f>
         <v>1980</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="s">
-        <v>379</v>
-      </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="42">
+      <c r="A18" s="57" t="s">
+        <v>364</v>
+      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="41">
         <f>F13*1.4</f>
         <v>7343.8399999999983</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
-        <v>380</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="34">
+      <c r="A19" s="57" t="s">
+        <v>365</v>
+      </c>
+      <c r="B19" s="56"/>
+      <c r="C19" s="33">
         <v>600000</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="58" t="s">
-        <v>381</v>
-      </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="43">
+      <c r="A20" s="57" t="s">
+        <v>366</v>
+      </c>
+      <c r="B20" s="56"/>
+      <c r="C20" s="42">
         <v>1.1499999999999999</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
-        <v>383</v>
-      </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="44">
+      <c r="A21" s="57" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="43">
         <f>C19/100*C20</f>
         <v>6899.9999999999991</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="67" t="s">
-        <v>384</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
+      <c r="A23" s="66" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="57"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="57"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
+      <c r="A25" s="56"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3604,55 +3734,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>385</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>386</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
+      <c r="A3" s="55" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="72" t="s">
-        <v>387</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="24" t="s">
-        <v>113</v>
+      <c r="A4" s="71" t="s">
+        <v>372</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="72" t="s">
-        <v>388</v>
-      </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="24" t="s">
-        <v>104</v>
+      <c r="A5" s="71" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="23" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="72" t="s">
-        <v>389</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="24" t="s">
-        <v>390</v>
+      <c r="A6" s="71" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="63"/>
+      <c r="C6" s="23" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="72" t="s">
-        <v>391</v>
-      </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="24" t="s">
-        <v>122</v>
+      <c r="A7" s="71" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="63"/>
+      <c r="C7" s="23" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3660,39 +3790,39 @@
       <c r="C8" s="11"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="66" t="s">
-        <v>392</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
+      <c r="A9" s="64" t="s">
+        <v>377</v>
+      </c>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="72" t="s">
-        <v>393</v>
-      </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="45">
+      <c r="A10" s="71" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="63"/>
+      <c r="C10" s="44">
         <f>'3. Income Statement'!B9</f>
         <v>1200000</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="72" t="s">
-        <v>394</v>
-      </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="24" t="s">
-        <v>395</v>
+      <c r="A11" s="71" t="s">
+        <v>379</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="23" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="72" t="s">
-        <v>396</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="24" t="s">
-        <v>395</v>
+      <c r="A12" s="71" t="s">
+        <v>381</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="23" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3700,29 +3830,29 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66" t="s">
-        <v>397</v>
-      </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
+      <c r="A14" s="64" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="72" t="s">
-        <v>398</v>
-      </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="46">
+      <c r="A15" s="71" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="63"/>
+      <c r="C15" s="45">
         <f>INDEX('Province Rate Reference'!$F$5:$F$17,MATCH('1. Entity Setup'!$C$12,'Province Rate Reference'!$A$5:$A$17,0))</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="72" t="s">
-        <v>399</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="47">
+      <c r="A16" s="71" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="46">
         <f>C10*C15</f>
         <v>60000</v>
       </c>
@@ -3732,62 +3862,62 @@
       <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="66" t="s">
-        <v>400</v>
-      </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
+      <c r="A18" s="64" t="s">
+        <v>385</v>
+      </c>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
     </row>
     <row r="19" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
-        <v>401</v>
-      </c>
-      <c r="C19" s="26">
+      <c r="A19" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="C19" s="25">
         <v>42000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="26">
+      <c r="A20" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="C20" s="25">
         <v>4000</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
-        <v>404</v>
-      </c>
-      <c r="C21" s="26">
+      <c r="A21" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="C21" s="25">
         <v>750</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="32" t="s">
-        <v>406</v>
-      </c>
-      <c r="C22" s="26">
+      <c r="A22" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="25">
         <v>1350</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
-      <c r="C23" s="29"/>
+      <c r="A23" s="30"/>
+      <c r="C23" s="28"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
-      <c r="C24" s="29"/>
+      <c r="A24" s="30"/>
+      <c r="C24" s="28"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C25" s="16">
         <f>SUM(C19:C24)</f>
@@ -3799,19 +3929,19 @@
       <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="66" t="s">
-        <v>408</v>
-      </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
+      <c r="A27" s="64" t="s">
+        <v>393</v>
+      </c>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B28" s="20"/>
-      <c r="C28" s="48">
+      <c r="C28" s="47">
         <f>C16-C25</f>
         <v>11900</v>
       </c>
@@ -3819,7 +3949,7 @@
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C29" s="9" t="str">
         <f>IF(C28&gt;3000,"Yes - instalments likely required","No")</f>
@@ -3828,12 +3958,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:D3"/>
@@ -3843,6 +3967,12 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3887,62 +4017,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>412</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
+      <c r="A3" s="55" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
     </row>
     <row r="4" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
-        <v>413</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="A4" s="65" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
-        <v>414</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="34">
+      <c r="A5" s="69" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="33">
         <v>28500</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="70" t="s">
-        <v>415</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="34">
+      <c r="A6" s="69" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="68"/>
+      <c r="C6" s="33">
         <v>12100</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="70" t="s">
-        <v>416</v>
-      </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="34">
+      <c r="A7" s="69" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="68"/>
+      <c r="C7" s="33">
         <v>24000</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="70" t="s">
-        <v>417</v>
-      </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="34">
+      <c r="A8" s="69" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="68"/>
+      <c r="C8" s="33">
         <v>10200</v>
       </c>
     </row>
@@ -3953,7 +4083,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="9" t="str">
@@ -3967,76 +4097,76 @@
       <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66" t="s">
-        <v>419</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
+      <c r="A12" s="64" t="s">
+        <v>404</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="B14" s="26">
+      <c r="A14" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="25">
         <v>10125</v>
       </c>
-      <c r="C14" s="30" t="s">
-        <v>423</v>
+      <c r="C14" s="29" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
-        <v>424</v>
-      </c>
-      <c r="B15" s="26">
+      <c r="A15" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="25">
         <v>10125</v>
       </c>
-      <c r="C15" s="30" t="s">
-        <v>423</v>
+      <c r="C15" s="29" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="B20" s="16">
         <f>SUM(B14:B19)</f>
@@ -4050,59 +4180,59 @@
       <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="66" t="s">
-        <v>426</v>
-      </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
+      <c r="A22" s="64" t="s">
+        <v>411</v>
+      </c>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="70" t="s">
-        <v>427</v>
-      </c>
-      <c r="B23" s="69"/>
-      <c r="C23" s="24" t="s">
-        <v>395</v>
+      <c r="A23" s="69" t="s">
+        <v>412</v>
+      </c>
+      <c r="B23" s="68"/>
+      <c r="C23" s="23" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="70" t="s">
-        <v>428</v>
-      </c>
-      <c r="B24" s="69"/>
-      <c r="C24" s="24" t="s">
-        <v>395</v>
+      <c r="A24" s="69" t="s">
+        <v>413</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="23" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="70" t="s">
-        <v>429</v>
-      </c>
-      <c r="B25" s="69"/>
-      <c r="C25" s="24" t="s">
-        <v>395</v>
+      <c r="A25" s="69" t="s">
+        <v>414</v>
+      </c>
+      <c r="B25" s="68"/>
+      <c r="C25" s="23" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="70" t="s">
-        <v>430</v>
-      </c>
-      <c r="B26" s="69"/>
-      <c r="C26" s="24" t="s">
-        <v>113</v>
+      <c r="A26" s="69" t="s">
+        <v>415</v>
+      </c>
+      <c r="B26" s="68"/>
+      <c r="C26" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="70" t="s">
-        <v>432</v>
-      </c>
-      <c r="B27" s="69"/>
-      <c r="C27" s="24" t="s">
-        <v>113</v>
+      <c r="A27" s="69" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" s="68"/>
+      <c r="C27" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4157,67 +4287,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>433</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>434</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
+      <c r="A3" s="55" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70" t="s">
-        <v>435</v>
-      </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="34">
+      <c r="A4" s="69" t="s">
+        <v>420</v>
+      </c>
+      <c r="B4" s="68"/>
+      <c r="C4" s="33">
         <v>65000</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
-        <v>436</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="49">
+      <c r="A5" s="69" t="s">
+        <v>421</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="48">
         <v>3000000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="53.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
-        <v>437</v>
+      <c r="A6" s="38" t="s">
+        <v>422</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="70" t="s">
-        <v>438</v>
-      </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="34">
+      <c r="A7" s="69" t="s">
+        <v>423</v>
+      </c>
+      <c r="B7" s="68"/>
+      <c r="C7" s="33">
         <v>240000</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="70" t="s">
-        <v>439</v>
-      </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="24" t="s">
-        <v>113</v>
+      <c r="A8" s="69" t="s">
+        <v>424</v>
+      </c>
+      <c r="B8" s="68"/>
+      <c r="C8" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="16">
@@ -4227,7 +4357,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="16">
@@ -4235,80 +4365,80 @@
         <v>22750</v>
       </c>
       <c r="D10" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
-        <v>441</v>
-      </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
+      <c r="A11" s="64" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63" t="s">
-        <v>442</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
+      <c r="A12" s="65" t="s">
+        <v>427</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="70" t="s">
-        <v>443</v>
-      </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="24" t="s">
-        <v>444</v>
+      <c r="A13" s="69" t="s">
+        <v>428</v>
+      </c>
+      <c r="B13" s="68"/>
+      <c r="C13" s="23" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="70" t="s">
-        <v>445</v>
-      </c>
-      <c r="B14" s="69"/>
-      <c r="C14" s="34">
+      <c r="A14" s="69" t="s">
+        <v>430</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="33">
         <v>9750</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="70" t="s">
-        <v>538</v>
-      </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="34"/>
+      <c r="A15" s="69" t="s">
+        <v>523</v>
+      </c>
+      <c r="B15" s="68"/>
+      <c r="C15" s="33"/>
       <c r="D15" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="66" t="s">
-        <v>446</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
+      <c r="A16" s="64" t="s">
+        <v>431</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>2025</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <v>8000</v>
       </c>
       <c r="C18" s="9">
@@ -4316,12 +4446,12 @@
         <v>2030</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="9">
         <f>IF(A19=0,0,A19+5)</f>
         <v>0</v>
@@ -4329,18 +4459,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4378,100 +4508,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>451</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>452</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="A3" s="55" t="s">
+        <v>437</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="C5" s="26">
+      <c r="A5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="25">
         <v>1000000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>35000</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="25">
         <v>18000</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="25">
         <v>6200</v>
       </c>
-      <c r="G5" s="30" t="s">
-        <v>460</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>461</v>
+      <c r="G5" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -4484,58 +4614,58 @@
       <c r="H8" s="11"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71" t="s">
-        <v>462</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="69"/>
+      <c r="A9" s="70" t="s">
+        <v>447</v>
+      </c>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="68"/>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="81" t="s">
-        <v>466</v>
+      <c r="H11" s="80" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="82"/>
+      <c r="H12" s="81"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
@@ -4545,61 +4675,61 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="83"/>
+      <c r="H13" s="82"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71" t="s">
-        <v>467</v>
-      </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="69"/>
+      <c r="A14" s="70" t="s">
+        <v>452</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="68"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="81" t="s">
-        <v>468</v>
-      </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="69"/>
+      <c r="A15" s="80" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="68"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="73"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="75"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="74"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="76"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="77"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="76"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="80"/>
+      <c r="A18" s="77"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4630,353 +4760,353 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>469</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
-        <v>470</v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
+      <c r="A2" s="58" t="s">
+        <v>455</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="50">
+        <v>0.23</v>
+      </c>
+      <c r="C5" s="50">
+        <v>0.11</v>
+      </c>
+      <c r="D5" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="F5" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="49" t="s">
+        <v>463</v>
+      </c>
+      <c r="B6" s="50">
+        <v>0.27</v>
+      </c>
+      <c r="C6" s="50">
+        <v>0.11</v>
+      </c>
+      <c r="D6" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>464</v>
+      </c>
+      <c r="F6" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="49" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" s="50">
+        <v>0.27</v>
+      </c>
+      <c r="C7" s="50">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>467</v>
+      </c>
+      <c r="F7" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
+        <v>469</v>
+      </c>
+      <c r="B8" s="50">
+        <v>0.27</v>
+      </c>
+      <c r="C8" s="50">
+        <v>0.09</v>
+      </c>
+      <c r="D8" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>470</v>
+      </c>
+      <c r="F8" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="50">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="C9" s="50">
+        <v>0.122</v>
+      </c>
+      <c r="D9" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E9" s="49" t="s">
         <v>472</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F9" s="52">
+        <v>0.13</v>
+      </c>
+      <c r="G9" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="49" t="s">
         <v>474</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="B10" s="50">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="C10" s="50">
+        <v>0.122</v>
+      </c>
+      <c r="D10" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E10" s="49" t="s">
         <v>475</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="51">
-        <v>0.23</v>
-      </c>
-      <c r="C5" s="51">
+      <c r="F10" s="52">
+        <v>0.14974999999999999</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="49" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" s="50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C11" s="50">
+        <v>0.115</v>
+      </c>
+      <c r="D11" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="F11" s="52">
+        <v>0.15</v>
+      </c>
+      <c r="G11" s="38"/>
+    </row>
+    <row r="12" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="49" t="s">
+        <v>478</v>
+      </c>
+      <c r="B12" s="50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C12" s="50">
+        <v>0.115</v>
+      </c>
+      <c r="D12" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="F12" s="52">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="49" t="s">
+        <v>480</v>
+      </c>
+      <c r="B13" s="50">
+        <v>0.31</v>
+      </c>
+      <c r="C13" s="50">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="F13" s="52">
+        <v>0.15</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="49" t="s">
+        <v>482</v>
+      </c>
+      <c r="B14" s="50">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="50">
+        <v>0.115</v>
+      </c>
+      <c r="D14" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="F14" s="52">
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="49" t="s">
+        <v>483</v>
+      </c>
+      <c r="B15" s="50">
+        <v>0.27</v>
+      </c>
+      <c r="C15" s="50">
+        <v>0.09</v>
+      </c>
+      <c r="D15" s="51">
+        <v>500000</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="F15" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="B16" s="50">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="C16" s="50">
         <v>0.11</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D16" s="51">
         <v>500000</v>
       </c>
-      <c r="E5" s="50" t="s">
-        <v>476</v>
-      </c>
-      <c r="F5" s="53">
+      <c r="E16" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="F16" s="52">
         <v>0.05</v>
       </c>
-      <c r="G5" s="39" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="B6" s="51">
+      <c r="G16" s="38"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="B17" s="50">
         <v>0.27</v>
       </c>
-      <c r="C6" s="51">
-        <v>0.11</v>
-      </c>
-      <c r="D6" s="52">
+      <c r="C17" s="50">
+        <v>0.12</v>
+      </c>
+      <c r="D17" s="51">
         <v>500000</v>
       </c>
-      <c r="E6" s="50" t="s">
-        <v>479</v>
-      </c>
-      <c r="F6" s="53">
+      <c r="E17" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="F17" s="52">
         <v>0.05</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="50" t="s">
-        <v>481</v>
-      </c>
-      <c r="B7" s="51">
-        <v>0.27</v>
-      </c>
-      <c r="C7" s="51">
-        <v>0.1</v>
-      </c>
-      <c r="D7" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>482</v>
-      </c>
-      <c r="F7" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
-        <v>484</v>
-      </c>
-      <c r="B8" s="51">
-        <v>0.27</v>
-      </c>
-      <c r="C8" s="51">
-        <v>0.09</v>
-      </c>
-      <c r="D8" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>485</v>
-      </c>
-      <c r="F8" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="50" t="s">
-        <v>374</v>
-      </c>
-      <c r="B9" s="51">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="C9" s="51">
-        <v>0.122</v>
-      </c>
-      <c r="D9" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E9" s="50" t="s">
+      <c r="G17" s="38"/>
+    </row>
+    <row r="19" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="66" t="s">
         <v>487</v>
       </c>
-      <c r="F9" s="53">
-        <v>0.13</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="50" t="s">
-        <v>489</v>
-      </c>
-      <c r="B10" s="51">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="C10" s="51">
-        <v>0.122</v>
-      </c>
-      <c r="D10" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>490</v>
-      </c>
-      <c r="F10" s="53">
-        <v>0.14974999999999999</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50" t="s">
-        <v>492</v>
-      </c>
-      <c r="B11" s="51">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="C11" s="51">
-        <v>0.115</v>
-      </c>
-      <c r="D11" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>487</v>
-      </c>
-      <c r="F11" s="53">
-        <v>0.15</v>
-      </c>
-      <c r="G11" s="39"/>
-    </row>
-    <row r="12" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="50" t="s">
-        <v>493</v>
-      </c>
-      <c r="B12" s="51">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="C12" s="51">
-        <v>0.115</v>
-      </c>
-      <c r="D12" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>487</v>
-      </c>
-      <c r="F12" s="53">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50" t="s">
-        <v>495</v>
-      </c>
-      <c r="B13" s="51">
-        <v>0.31</v>
-      </c>
-      <c r="C13" s="51">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E13" s="50" t="s">
-        <v>487</v>
-      </c>
-      <c r="F13" s="53">
-        <v>0.15</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="50" t="s">
-        <v>497</v>
-      </c>
-      <c r="B14" s="51">
-        <v>0.3</v>
-      </c>
-      <c r="C14" s="51">
-        <v>0.115</v>
-      </c>
-      <c r="D14" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>487</v>
-      </c>
-      <c r="F14" s="53">
-        <v>0.15</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="50" t="s">
-        <v>498</v>
-      </c>
-      <c r="B15" s="51">
-        <v>0.27</v>
-      </c>
-      <c r="C15" s="51">
-        <v>0.09</v>
-      </c>
-      <c r="D15" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E15" s="50" t="s">
-        <v>476</v>
-      </c>
-      <c r="F15" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50" t="s">
-        <v>500</v>
-      </c>
-      <c r="B16" s="51">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="C16" s="51">
-        <v>0.11</v>
-      </c>
-      <c r="D16" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E16" s="50" t="s">
-        <v>476</v>
-      </c>
-      <c r="F16" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="G16" s="39"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50" t="s">
-        <v>501</v>
-      </c>
-      <c r="B17" s="51">
-        <v>0.27</v>
-      </c>
-      <c r="C17" s="51">
-        <v>0.12</v>
-      </c>
-      <c r="D17" s="52">
-        <v>500000</v>
-      </c>
-      <c r="E17" s="50" t="s">
-        <v>476</v>
-      </c>
-      <c r="F17" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="G17" s="39"/>
-    </row>
-    <row r="19" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="67" t="s">
-        <v>502</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4998,253 +5128,253 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>503</v>
-      </c>
-      <c r="C1" s="54" t="s">
-        <v>285</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>363</v>
-      </c>
-      <c r="E1" s="54" t="s">
-        <v>504</v>
-      </c>
-      <c r="F1" s="54" t="s">
-        <v>329</v>
-      </c>
-      <c r="G1" s="54" t="s">
-        <v>322</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>323</v>
-      </c>
-      <c r="I1" s="54" t="s">
-        <v>505</v>
-      </c>
-      <c r="J1" s="54" t="s">
-        <v>506</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>507</v>
+      <c r="A1" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>488</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="H1" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="I1" s="53" t="s">
+        <v>490</v>
+      </c>
+      <c r="J1" s="53" t="s">
+        <v>491</v>
+      </c>
+      <c r="K1" s="53" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -5258,7 +5388,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5268,28 +5398,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -5332,12 +5462,12 @@
       <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
@@ -5374,12 +5504,12 @@
       <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
@@ -5390,75 +5520,78 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="B17" s="14">
+        <f>IF(SUMPRODUCT(--('3. Income Statement'!B52:B60&lt;&gt;0))&gt;0,'3. Income Statement'!B52+'3. Income Statement'!B53+'3. Income Statement'!B54+'3. Income Statement'!B55,'3. Income Statement'!B48)</f>
+        <v>55000</v>
+      </c>
+      <c r="C17" s="83" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="B18" s="16">
+        <f>MIN(500000,MAX(0,(IF('5. Prior-Year Tax Attributes'!C30="",B17,'5. Prior-Year Tax Attributes'!C30)-50000)*5))</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" s="14">
-        <f>'3. Income Statement'!B48</f>
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="16">
-        <f>MIN(500000,MAX(0,(B17-50000)*5))</f>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>60</v>
       </c>
       <c r="B19" s="14">
         <f>'7. Associated Corporations'!E10</f>
         <v>1565000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="16">
         <f>MIN(500000,MAX(0,(B19-10000000)/40000000*500000))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
-        <v>62</v>
+    <row r="21" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A21" s="84" t="s">
+        <v>60</v>
       </c>
       <c r="B21" s="16">
         <f>MAX(0,500000-MAX(B18,B20))</f>
         <v>475000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
-        <v>63</v>
+    <row r="22" spans="1:4" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="84" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="16">
-        <f>MIN(B21,IF('1. Entity Setup'!$C$28="Yes",IFERROR(VLOOKUP("Northern Peak Consulting Inc. (this entity)",'7. Associated Corporations'!A5:F9,6,FALSE()),500000),500000))</f>
+        <f>MIN(B21,IF('1. Entity Setup'!$C$28="Yes",IFERROR(VLOOKUP("*"&amp;B5&amp;"*",'7. Associated Corporations'!A5:F9,6,FALSE()),500000),500000))</f>
         <v>350000</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>64</v>
+      <c r="C22" s="83" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
-        <v>65</v>
+      <c r="A23" s="85" t="s">
+        <v>62</v>
       </c>
       <c r="B23" s="16">
         <f>MIN(B16,B22)</f>
         <v>190000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
-        <v>66</v>
+    <row r="24" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A24" s="85" t="s">
+        <v>63</v>
       </c>
       <c r="B24" s="16">
         <f>MAX(0,B16-B22)</f>
@@ -5467,7 +5600,7 @@
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B25" s="9" t="str">
         <f>IF(B18&gt;0,"GRINDING — AAII over $50,000","OK — under $50,000 threshold")</f>
@@ -5479,299 +5612,720 @@
       <c r="B26" s="11"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="16">
+      <c r="A27" s="64" t="s">
+        <v>529</v>
+      </c>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+    </row>
+    <row r="28" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A28" s="85" t="s">
+        <v>530</v>
+      </c>
+      <c r="B28" s="9" t="str">
+        <f>IF(SUMPRODUCT(--('3. Income Statement'!B52:B60&lt;&gt;0))&gt;0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="C28" s="83" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A29" s="85" t="s">
+        <v>532</v>
+      </c>
+      <c r="B29" s="16">
+        <f>IF(B28="Yes",'3. Income Statement'!B52+'3. Income Statement'!B53,'3. Income Statement'!B48)</f>
+        <v>55000</v>
+      </c>
+      <c r="C29" s="83" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="85" t="s">
+        <v>534</v>
+      </c>
+      <c r="B30" s="16">
+        <f>IF(B28="Yes",'3. Income Statement'!B54+'3. Income Statement'!B55,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="85" t="s">
+        <v>535</v>
+      </c>
+      <c r="B31" s="16">
+        <f>IF(B28="Yes",'3. Income Statement'!B56+'3. Income Statement'!B57,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="B32" s="16">
+        <f>B30*0.383333333333</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A33" s="85" t="s">
+        <v>537</v>
+      </c>
+      <c r="B33" s="16">
+        <f>IF(B28="Yes",'3. Income Statement'!B58+'3. Income Statement'!B59,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="86" t="s">
+        <v>538</v>
+      </c>
+      <c r="B34" s="19">
+        <f>B32+B33</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="85" t="s">
+        <v>539</v>
+      </c>
+      <c r="B35" s="16">
+        <f>IF(B28="Yes",'3. Income Statement'!B53,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="83" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="64" t="s">
+        <v>541</v>
+      </c>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="85" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="16">
         <f>B23*B11</f>
         <v>20900</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="16">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="16">
         <f>B24*B12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="16">
-        <f>B17*B13</f>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="85" t="s">
+        <v>542</v>
+      </c>
+      <c r="B40" s="16">
+        <f>B29*B13</f>
         <v>25668.5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="19">
-        <f>B28+B29+B30</f>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="86" t="s">
+        <v>543</v>
+      </c>
+      <c r="B41" s="19">
+        <f>B38+B39+B40</f>
         <v>46568.5</v>
       </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="14">
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="85" t="s">
+        <v>544</v>
+      </c>
+      <c r="B42" s="16">
+        <f>B34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A43" s="85" t="s">
+        <v>545</v>
+      </c>
+      <c r="B43" s="16">
+        <f>0.2*B78</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="83" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A44" s="85" t="s">
+        <v>547</v>
+      </c>
+      <c r="B44" s="16">
+        <f>0.6*B80</f>
+        <v>0</v>
+      </c>
+      <c r="C44" s="83" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="86" t="s">
+        <v>549</v>
+      </c>
+      <c r="B45" s="19">
+        <f>B41+B42+B43+B44</f>
+        <v>46568.5</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="85" t="s">
+        <v>550</v>
+      </c>
+      <c r="B46" s="16">
+        <f>B75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A47" s="85" t="s">
+        <v>551</v>
+      </c>
+      <c r="B47" s="16">
+        <f>MIN('12. Credits &amp; Incentives'!C9+'12. Credits &amp; Incentives'!C14,MAX(0,B41))</f>
+        <v>32500</v>
+      </c>
+      <c r="C47" s="83" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="85" t="s">
+        <v>553</v>
+      </c>
+      <c r="B48" s="16">
+        <f>('12. Credits &amp; Incentives'!C10+'12. Credits &amp; Incentives'!C15)-(B47-MIN(('12. Credits &amp; Incentives'!C9-'12. Credits &amp; Incentives'!C10)+('12. Credits &amp; Incentives'!C14-'12. Credits &amp; Incentives'!C15),MAX(0,B41)))</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="83" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="86" t="s">
+        <v>555</v>
+      </c>
+      <c r="B49" s="19">
+        <f>B45-B46-B47-B48</f>
+        <v>14068.5</v>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="85" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="16">
         <f>'11. Instalments &amp; Compliance'!B20</f>
         <v>20250</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="21">
-        <f>B31-B32</f>
-        <v>26318.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="9" t="str">
-        <f>IF(B31&gt;3000,"Yes","No")</f>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="21">
+        <f>B49-B50</f>
+        <v>-6181.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A52" s="85" t="s">
+        <v>556</v>
+      </c>
+      <c r="B52" s="16">
+        <f>(('12. Credits &amp; Incentives'!C9-'12. Credits &amp; Incentives'!C10)+('12. Credits &amp; Incentives'!C14-'12. Credits &amp; Incentives'!C15))-MIN(('12. Credits &amp; Incentives'!C9-'12. Credits &amp; Incentives'!C10)+('12. Credits &amp; Incentives'!C14-'12. Credits &amp; Incentives'!C15),MAX(0,B41))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="9" t="str">
+        <f>IF(B41&gt;3000,"Yes","No")</f>
         <v>Yes</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-    </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-    </row>
-    <row r="37" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" s="16">
-        <f>B17*0.3067</f>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="64" t="s">
+        <v>557</v>
+      </c>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+    </row>
+    <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A56" s="85" t="s">
+        <v>558</v>
+      </c>
+      <c r="B56" s="16">
+        <f>B29*0.3067+IF(B28="Yes",'3. Income Statement'!B55*0.383333333333+'3. Income Statement'!B59,0)</f>
         <v>16868.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="14">
+    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="16">
         <f>'5. Prior-Year Tax Attributes'!C6</f>
         <v>42300</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="16">
-        <f>B38+B37</f>
+    <row r="58" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A58" s="85" t="s">
+        <v>559</v>
+      </c>
+      <c r="B58" s="16">
+        <f>B57+B56</f>
         <v>59168.5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="14">
+    <row r="59" spans="1:4" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A59" s="85" t="s">
+        <v>560</v>
+      </c>
+      <c r="B59" s="16">
+        <f>IF(B28="Yes",'3. Income Statement'!B54*0.383333333333+'3. Income Statement'!B58,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="B60" s="16">
         <f>'5. Prior-Year Tax Attributes'!C5</f>
         <v>18500</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="16">
-        <f>B39/0.3833</f>
-        <v>154366.0318288547</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="16">
-        <f>B40/0.3833</f>
-        <v>48265.066527524134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="14">
-        <f>'5. Prior-Year Tax Attributes'!C9</f>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="85" t="s">
+        <v>561</v>
+      </c>
+      <c r="B61" s="16">
+        <f>B60+B59</f>
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A62" s="85" t="s">
+        <v>562</v>
+      </c>
+      <c r="B62" s="16">
+        <f>0.72*B24+IF(B28="Yes",'3. Income Statement'!B54+'3. Income Statement'!B56,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="85" t="s">
+        <v>563</v>
+      </c>
+      <c r="B63" s="16">
+        <f>'5. Prior-Year Tax Attributes'!C9+B62</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="14">
-        <f>'5. Prior-Year Tax Attributes'!C12</f>
+    <row r="64" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A64" s="85" t="s">
+        <v>564</v>
+      </c>
+      <c r="B64" s="16">
+        <f>B35+IF(B28="Yes",'3. Income Statement'!B60,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="85" t="s">
+        <v>565</v>
+      </c>
+      <c r="B65" s="16">
+        <f>'5. Prior-Year Tax Attributes'!C12+B64</f>
         <v>22000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" s="22" t="str">
-        <f>IF(B44&gt;0,"CDA balance sitting idle — consider a capital dividend election","No CDA balance available")</f>
+    <row r="66" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A66" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="16">
+        <f>B58/0.383333333333</f>
+        <v>154352.60869578639</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A67" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="16">
+        <f>B61/0.383333333333</f>
+        <v>48260.869565259352</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="64" t="s">
+        <v>566</v>
+      </c>
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+    </row>
+    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="B70" s="16">
+        <f>'3. Income Statement'!B63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="85" t="s">
+        <v>204</v>
+      </c>
+      <c r="B71" s="16">
+        <f>'3. Income Statement'!B64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="85" t="s">
+        <v>567</v>
+      </c>
+      <c r="B72" s="16">
+        <f>'3. Income Statement'!B65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A73" s="85" t="s">
+        <v>568</v>
+      </c>
+      <c r="B73" s="16">
+        <f>MIN(B71*0.383333333333,B58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A74" s="85" t="s">
+        <v>569</v>
+      </c>
+      <c r="B74" s="16">
+        <f>MIN(B70*0.383333333333,B61)+MIN(B71*0.383333333333-B73,B61-MIN(B70*0.383333333333,B61))</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="83" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="86" t="s">
+        <v>571</v>
+      </c>
+      <c r="B75" s="19">
+        <f>B73+B74</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+    </row>
+    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="85" t="s">
+        <v>572</v>
+      </c>
+      <c r="B76" s="16">
+        <f>B58-B73</f>
+        <v>59168.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="85" t="s">
+        <v>573</v>
+      </c>
+      <c r="B77" s="16">
+        <f>B61-B74</f>
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A78" s="85" t="s">
+        <v>574</v>
+      </c>
+      <c r="B78" s="16">
+        <f>MAX(0,B70-B63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="85" t="s">
+        <v>575</v>
+      </c>
+      <c r="B79" s="16">
+        <f>MAX(0,B63-B70)</f>
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A80" s="85" t="s">
+        <v>576</v>
+      </c>
+      <c r="B80" s="16">
+        <f>MAX(0,B72-B65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="85" t="s">
+        <v>577</v>
+      </c>
+      <c r="B81" s="16">
+        <f>MAX(0,B65-B72)</f>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="B82" s="22" t="str">
+        <f>IF(B81&gt;0,"CDA balance sitting idle — consider a capital dividend election","No unused CDA balance")</f>
         <v>CDA balance sitting idle — consider a capital dividend election</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-    </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="14">
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="64" t="s">
+        <v>578</v>
+      </c>
+      <c r="B84" s="63"/>
+      <c r="C84" s="63"/>
+      <c r="D84" s="63"/>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" s="16">
         <f>'9. Payroll Register'!C13</f>
         <v>600000</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="14">
+    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="16">
         <f>'9. Payroll Register'!C18</f>
         <v>7343.8399999999983</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="23">
+    <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" s="21">
         <f>'10. GST-HST'!C28</f>
         <v>11900</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="14">
+    <row r="88" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A88" s="85" t="s">
+        <v>77</v>
+      </c>
+      <c r="B88" s="16">
         <f>'6. CCA Continuity'!H13</f>
         <v>36900</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="14">
+    <row r="89" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A89" s="85" t="s">
+        <v>579</v>
+      </c>
+      <c r="B89" s="16">
         <f>'12. Credits &amp; Incentives'!C9</f>
         <v>22750</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" s="14">
+    <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="B90" s="16">
         <f>'12. Credits &amp; Incentives'!C14</f>
         <v>9750</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-    </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="64"/>
-      <c r="C55" s="64"/>
-      <c r="D55" s="64"/>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="65" t="str">
+    <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="64" t="s">
+        <v>580</v>
+      </c>
+      <c r="B92" s="63"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="63"/>
+    </row>
+    <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="62" t="str">
         <f>IF(B18&gt;0,"• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.","")</f>
         <v>• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.</v>
       </c>
-      <c r="B56" s="64"/>
-      <c r="C56" s="64"/>
-      <c r="D56" s="64"/>
-    </row>
-    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="65" t="str">
+      <c r="B93" s="63"/>
+      <c r="C93" s="63"/>
+      <c r="D93" s="63"/>
+    </row>
+    <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="62" t="str">
         <f>IF(COUNTIF('8. Shareholders &amp; TOSI'!I5:I20,"Not Excluded - TOSI Risk")&gt;0,"• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.","")</f>
         <v>• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.</v>
       </c>
-      <c r="B57" s="64"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-    </row>
-    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="65" t="str">
-        <f>IF(B44&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
+      <c r="B94" s="63"/>
+      <c r="C94" s="63"/>
+      <c r="D94" s="63"/>
+    </row>
+    <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="62" t="str">
+        <f>IF(B81&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
         <v>• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.</v>
       </c>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-    </row>
-    <row r="59" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" s="64"/>
-      <c r="C59" s="64"/>
-      <c r="D59" s="64"/>
-    </row>
+      <c r="B95" s="63"/>
+      <c r="C95" s="63"/>
+      <c r="D95" s="63"/>
+    </row>
+    <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="62" t="str">
+        <f>IF(AND(B18&gt;0,'5. Prior-Year Tax Attributes'!C30=""),"• SBD grind uses current-year investment income as a proxy — enter the prior-year adjusted AAII on '5. Prior-Year Tax Attributes'.","")</f>
+        <v>• SBD grind uses current-year investment income as a proxy — enter the prior-year adjusted AAII on '5. Prior-Year Tax Attributes'.</v>
+      </c>
+      <c r="B96" s="63"/>
+      <c r="C96" s="63"/>
+      <c r="D96" s="63"/>
+    </row>
+    <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="62" t="str">
+        <f>IF(B34&gt;B75,"• Part IV tax exceeds this year's dividend refund — the difference sits in RDTOH until taxable dividends are paid.","")</f>
+        <v/>
+      </c>
+      <c r="B97" s="63"/>
+      <c r="C97" s="63"/>
+      <c r="D97" s="63"/>
+    </row>
+    <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="62" t="str">
+        <f>IF(B78&gt;0,"• Eligible dividends exceed GRIP — Part III.1 tax applies unless the s.185.1(2) election is filed.","")</f>
+        <v/>
+      </c>
+      <c r="B98" s="63"/>
+      <c r="C98" s="63"/>
+      <c r="D98" s="63"/>
+    </row>
+    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="62" t="str">
+        <f>IF(B80&gt;0,"• Capital dividend exceeds the CDA — 60% Part III tax unless the s.184(3) election is filed.","")</f>
+        <v/>
+      </c>
+      <c r="B99" s="63"/>
+      <c r="C99" s="63"/>
+      <c r="D99" s="63"/>
+    </row>
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="62" t="str">
+        <f>IF(B52&gt;0,"• Non-refundable credits exceed Part I tax — the excess carries forward and is NOT in the year-end balance.","")</f>
+        <v/>
+      </c>
+      <c r="B100" s="63"/>
+      <c r="C100" s="63"/>
+      <c r="D100" s="63"/>
+    </row>
+    <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="62" t="str">
+        <f>IF(B48&gt;0,"• Refundable credits exceed Part I tax — the cash refund depends on CRA / the province accepting the claim.","")</f>
+        <v/>
+      </c>
+      <c r="B101" s="63"/>
+      <c r="C101" s="63"/>
+      <c r="D101" s="63"/>
+    </row>
+    <row r="102" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" s="63"/>
+      <c r="C102" s="63"/>
+      <c r="D102" s="63"/>
+    </row>
+    <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="21">
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5793,232 +6347,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="56"/>
+      <c r="C4" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="56"/>
+      <c r="C5" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="56"/>
+      <c r="C6" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="56"/>
+      <c r="C7" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="56"/>
+      <c r="C8" s="23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="56"/>
+      <c r="C11" s="23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
+      <c r="B12" s="56"/>
+      <c r="C12" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="24" t="s">
+      <c r="B13" s="56"/>
+      <c r="C13" s="23" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+      <c r="D13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="24" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="55" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="58" t="s">
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="24" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="23" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="58" t="s">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="24" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="23" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58" t="s">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="24" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="57" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="56" t="s">
+      <c r="B19" s="56"/>
+      <c r="C19" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="58" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="24" t="s">
+      <c r="B20" s="56"/>
+      <c r="C20" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="57" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="58" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="57" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
+      <c r="B24" s="56"/>
+      <c r="C24" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="24" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="B25" s="56"/>
+      <c r="C25" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56" t="s">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="24" t="s">
+      <c r="B28" s="56"/>
+      <c r="C28" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="58" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="24">
+      <c r="B29" s="56"/>
+      <c r="C29" s="23">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A5:B5"/>
@@ -6031,18 +6597,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6090,63 +6644,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="67" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="A2" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="26">
+      <c r="A5" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="25">
         <v>850000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>420000</v>
       </c>
       <c r="D5" s="12">
@@ -6165,18 +6719,18 @@
         <f>F5*'3. Income Statement'!$B$49</f>
         <v>200687.49999999997</v>
       </c>
-      <c r="H5" s="27" t="s">
-        <v>145</v>
+      <c r="H5" s="26" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="26">
+      <c r="A6" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="25">
         <v>350000</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>180000</v>
       </c>
       <c r="D6" s="12">
@@ -6195,14 +6749,14 @@
         <f>F6*'3. Income Statement'!$B$49</f>
         <v>84312.5</v>
       </c>
-      <c r="H6" s="27" t="s">
-        <v>147</v>
+      <c r="H6" s="26" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
       <c r="D7" s="12">
         <f t="shared" ref="D7:D12" si="1">IF(SUM($B$7:$B$12)=0,0,B7/SUM($B$7:$B$12))</f>
         <v>0</v>
@@ -6219,12 +6773,12 @@
         <f>F7*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H7" s="28"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6241,12 +6795,12 @@
         <f>F8*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6263,12 +6817,12 @@
         <f>F9*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6285,12 +6839,12 @@
         <f>F10*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6307,12 +6861,12 @@
         <f>F11*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6329,11 +6883,11 @@
         <f>F12*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B14" s="16">
         <f>SUM(B5:B12)</f>
@@ -6350,8 +6904,8 @@
         <v>1</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="27" t="s">
-        <v>149</v>
+      <c r="H14" s="26" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -6394,62 +6948,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="A4" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="29">
         <v>850000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="30">
+      <c r="A6" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="29">
         <v>350000</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="68"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68"/>
-      <c r="B8" s="69"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B9" s="9">
         <f>SUM(B5:B8)</f>
@@ -6461,28 +7015,28 @@
       <c r="B10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
-        <v>158</v>
-      </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
+      <c r="A11" s="64" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="30">
+      <c r="A12" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="29">
         <v>180000</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
-      <c r="B13" s="28"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="27"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B14" s="9">
         <f>SUM(B12:B13)</f>
@@ -6491,7 +7045,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B15" s="9">
         <f>B9-B14</f>
@@ -6503,118 +7057,118 @@
       <c r="B16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
+      <c r="A17" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="B18" s="30">
+      <c r="A18" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="29">
         <v>600000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="B19" s="30">
+      <c r="A19" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="29">
         <v>60000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="30">
+      <c r="A20" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="29">
         <v>25000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="29">
         <v>8000</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="29">
         <v>15000</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" s="30">
+      <c r="A23" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="29">
         <v>10000</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="29">
         <v>45000</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="29">
         <v>30000</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="30">
+      <c r="A26" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="29">
         <v>20000</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="29">
         <v>12000</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
-      <c r="B29" s="28"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="27"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="31"/>
-      <c r="B30" s="28"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="27"/>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B31" s="9">
         <f>SUM(B18:B30)</f>
@@ -6623,7 +7177,7 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B32" s="9">
         <f>B15-B31</f>
@@ -6635,104 +7189,104 @@
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
+      <c r="A34" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="B35" s="30">
+      <c r="A35" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="29">
         <v>12000</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="B36" s="30">
+      <c r="A36" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="29">
         <v>40000</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B37" s="30">
+      <c r="A37" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="29">
         <v>15000</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="30">
+      <c r="A38" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="29">
         <v>20000</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="B39" s="30">
+      <c r="A39" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="29">
         <v>8000</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="B40" s="30">
+      <c r="A40" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="29">
         <v>0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="31"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="31"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B43" s="9">
         <f>SUM(B35:B42)</f>
@@ -6741,7 +7295,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B44" s="18">
         <f>B32+B43</f>
@@ -6755,16 +7309,16 @@
       <c r="B45" s="11"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="B46" s="64"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
+      <c r="A46" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B47" s="9">
         <f>B32</f>
@@ -6773,7 +7327,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B48" s="9">
         <f>SUMIF(C35:C42,"Aggregate Investment Income",B35:B42)</f>
@@ -6782,7 +7336,7 @@
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <f>B44</f>
@@ -6791,126 +7345,126 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B51" s="55"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="55"/>
+        <v>182</v>
+      </c>
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B52" s="30"/>
+        <v>183</v>
+      </c>
+      <c r="B52" s="29"/>
       <c r="D52" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B53" s="30"/>
+        <v>185</v>
+      </c>
+      <c r="B53" s="29"/>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="B54" s="30"/>
+        <v>187</v>
+      </c>
+      <c r="B54" s="29"/>
       <c r="D54" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="B55" s="30"/>
+        <v>189</v>
+      </c>
+      <c r="B55" s="29"/>
       <c r="D55" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="B56" s="30"/>
+        <v>191</v>
+      </c>
+      <c r="B56" s="29"/>
       <c r="D56" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B57" s="30"/>
+        <v>193</v>
+      </c>
+      <c r="B57" s="29"/>
       <c r="D57" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="B58" s="30"/>
+        <v>195</v>
+      </c>
+      <c r="B58" s="29"/>
       <c r="D58" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B59" s="30"/>
+        <v>197</v>
+      </c>
+      <c r="B59" s="29"/>
       <c r="D59" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B60" s="30"/>
+        <v>199</v>
+      </c>
+      <c r="B60" s="29"/>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="B62" s="55"/>
-      <c r="C62" s="55"/>
-      <c r="D62" s="55"/>
+        <v>201</v>
+      </c>
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="B63" s="30"/>
+        <v>202</v>
+      </c>
+      <c r="B63" s="29"/>
       <c r="D63" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="B64" s="30"/>
+        <v>204</v>
+      </c>
+      <c r="B64" s="29"/>
       <c r="D64" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="B65" s="30"/>
+        <v>206</v>
+      </c>
+      <c r="B65" s="29"/>
       <c r="D65" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -6959,120 +7513,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="A4" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="26">
+      <c r="A5" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="25">
         <v>145000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="26">
+      <c r="A6" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="25">
         <v>210000</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="26">
+      <c r="A8" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="25">
         <v>15000</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="26">
+      <c r="A9" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="25">
         <v>380000</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="A10" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="25">
         <v>260000</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="A11" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="25">
         <v>100000</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="A12" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="25">
         <v>35000</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="28"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="28"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B15" s="16">
         <f>SUM(B5:B14)</f>
@@ -7081,89 +7635,89 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
-      <c r="B16" s="33"/>
+      <c r="B16" s="32"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
+      <c r="A17" s="64" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="26">
+      <c r="A18" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="25">
         <v>95000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="26">
+      <c r="A19" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="25">
         <v>12000</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="B20" s="26">
+      <c r="A20" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="25">
         <v>40000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="B21" s="26">
+      <c r="A21" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="25">
         <v>25000</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" s="26">
+      <c r="A22" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="25">
         <v>30000</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="26">
+      <c r="A23" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="25">
         <v>150000</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="26">
+      <c r="A24" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="25">
         <v>20000</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="31"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="28"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
-      <c r="B26" s="29"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="28"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B27" s="16">
         <f>SUM(B18:B26)</f>
@@ -7172,43 +7726,43 @@
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="33"/>
+      <c r="B28" s="32"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="66" t="s">
-        <v>249</v>
-      </c>
-      <c r="B29" s="64"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
+      <c r="A29" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="B30" s="26">
+      <c r="A30" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="25">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="B31" s="26">
+      <c r="A31" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="25">
         <v>90000</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="B32" s="26">
+      <c r="A32" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="25">
         <v>397900</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
-        <v>253</v>
+      <c r="A33" s="24" t="s">
+        <v>238</v>
       </c>
       <c r="B33" s="14">
         <f>'3. Income Statement'!B49</f>
@@ -7217,7 +7771,7 @@
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B34" s="16">
         <f>SUM(B30:B33)</f>
@@ -7226,11 +7780,11 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="B35" s="33"/>
+      <c r="B35" s="32"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="17" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="B36" s="16">
         <f>B27+B34</f>
@@ -7239,7 +7793,7 @@
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B37" s="16">
         <f>B15-(B27+B34)</f>
@@ -7248,35 +7802,35 @@
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
-      <c r="B38" s="33"/>
+      <c r="B38" s="32"/>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="66" t="s">
-        <v>257</v>
-      </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
+      <c r="A39" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
     </row>
     <row r="40" spans="1:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="B40" s="33"/>
+      <c r="A40" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B40" s="32"/>
       <c r="D40" s="13" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B41" s="16">
         <f>B15</f>
         <v>1145000</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -7307,51 +7861,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>262</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
-        <v>263</v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
+      <c r="A2" s="58" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="A4" s="64" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="34">
+      <c r="A5" s="69" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="33">
         <v>18500</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="34">
+      <c r="A6" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="68"/>
+      <c r="C6" s="33">
         <v>42300</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7360,23 +7914,23 @@
       <c r="C7" s="11"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="66" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
+      <c r="A8" s="64" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="70" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="34">
+      <c r="A9" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="68"/>
+      <c r="C9" s="33">
         <v>65000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7385,23 +7939,23 @@
       <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
+      <c r="A11" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="70" t="s">
-        <v>272</v>
-      </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="34">
+      <c r="A12" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="68"/>
+      <c r="C12" s="33">
         <v>22000</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7410,32 +7964,32 @@
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
+      <c r="A14" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>2022</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>15000</v>
       </c>
       <c r="C16" s="9">
@@ -7444,24 +7998,24 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="9">
         <f>IF(A17=0,0,A17+20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="9">
         <f>IF(A18=0,0,A18+20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="9">
         <f>IF(A19=0,0,A19+20)</f>
         <v>0</v>
@@ -7473,33 +8027,33 @@
       <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="66" t="s">
-        <v>277</v>
-      </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
+      <c r="A21" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
       <c r="C23" s="11"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
       <c r="C24" s="11"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7508,51 +8062,45 @@
       <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="66" t="s">
-        <v>278</v>
-      </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
+      <c r="A26" s="64" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="B27" s="69"/>
-      <c r="C27" s="34">
+      <c r="A27" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="68"/>
+      <c r="C27" s="33">
         <v>0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="34">
+      <c r="A28" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="B28" s="68"/>
+      <c r="C28" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C30" s="34"/>
+        <v>267</v>
+      </c>
+      <c r="C30" s="33"/>
       <c r="D30" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
@@ -7561,6 +8109,12 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7586,54 +8140,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>284</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
-        <v>294</v>
+      <c r="A4" s="34" t="s">
+        <v>279</v>
       </c>
       <c r="B4" s="5">
         <v>180000</v>
@@ -7642,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -7651,7 +8205,7 @@
         <f t="shared" ref="F4:F12" si="0">B4+C4-E4-IF(D4="Yes",0,C4*0.5)</f>
         <v>180000</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="35">
         <v>0.04</v>
       </c>
       <c r="H4" s="4">
@@ -7663,12 +8217,12 @@
         <v>172800</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
-        <v>296</v>
+      <c r="A5" s="34" t="s">
+        <v>281</v>
       </c>
       <c r="B5" s="5">
         <v>45000</v>
@@ -7677,7 +8231,7 @@
         <v>12000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
@@ -7686,7 +8240,7 @@
         <f t="shared" si="0"/>
         <v>51000</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="35">
         <v>0.2</v>
       </c>
       <c r="H5" s="4">
@@ -7698,12 +8252,12 @@
         <v>46800</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>298</v>
+      <c r="A6" s="34" t="s">
+        <v>283</v>
       </c>
       <c r="B6" s="5">
         <v>22000</v>
@@ -7712,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -7721,7 +8275,7 @@
         <f t="shared" si="0"/>
         <v>22000</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="35">
         <v>0.3</v>
       </c>
       <c r="H6" s="4">
@@ -7735,8 +8289,8 @@
       <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>299</v>
+      <c r="A7" s="34" t="s">
+        <v>284</v>
       </c>
       <c r="B7" s="5">
         <v>8000</v>
@@ -7745,7 +8299,7 @@
         <v>15000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E7" s="5">
         <v>0</v>
@@ -7754,7 +8308,7 @@
         <f t="shared" si="0"/>
         <v>23000</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="35">
         <v>0.55000000000000004</v>
       </c>
       <c r="H7" s="4">
@@ -7766,12 +8320,12 @@
         <v>10349.999999999998</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
-        <v>301</v>
+      <c r="A8" s="34" t="s">
+        <v>286</v>
       </c>
       <c r="B8" s="5">
         <v>5000</v>
@@ -7780,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -7789,7 +8343,7 @@
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="35">
         <v>0.05</v>
       </c>
       <c r="H8" s="4">
@@ -7801,20 +8355,20 @@
         <v>4750</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="37"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7823,19 +8377,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="27"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="37"/>
+      <c r="G10" s="36"/>
       <c r="H10" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7844,19 +8398,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="28"/>
+      <c r="J10" s="27"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
       <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7865,19 +8419,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J11" s="28"/>
+      <c r="J11" s="27"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="37"/>
+      <c r="G12" s="36"/>
       <c r="H12" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7886,11 +8440,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J12" s="28"/>
+      <c r="J12" s="27"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="16">
         <f>SUM(B4:B12)</f>
@@ -7918,42 +8472,42 @@
       <c r="J13" s="11"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="67" t="s">
-        <v>303</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
+      <c r="A15" s="66" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
+      <c r="A17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8005,58 +8559,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
-        <v>304</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
-        <v>305</v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
+      <c r="A2" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="C5" s="38">
+      <c r="A5" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="10">
@@ -8067,66 +8621,66 @@
         <f>'4. Balance Sheet'!B41</f>
         <v>1145000</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>350000</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>314</v>
+      <c r="G5" s="26" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="38">
+      <c r="A6" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="37">
         <v>1</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>60000</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>420000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>150000</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>317</v>
+      <c r="G6" s="38" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="28"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="28"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="28"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -8145,14 +8699,14 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>318</v>
+      <c r="A11" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="40">
+      <c r="F11" s="39">
         <f>F10-500000</f>
         <v>0</v>
       </c>
@@ -8168,12 +8722,12 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="70" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="24" t="s">
-        <v>113</v>
+      <c r="A13" s="69" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="68"/>
+      <c r="C13" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
